--- a/outputs/tablestat_template.xlsx
+++ b/outputs/tablestat_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\BELANDA\PhD Thesis\Code\MATLAB\amode_navigation_experiment\experiment_b\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC2A7B3-DC7B-4FED-A640-7620AA6C5F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373B26CE-338E-419B-AB41-19D3BBCC2BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{B592097C-7DAF-4CBB-990E-BEE084540A4C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B592097C-7DAF-4CBB-990E-BEE084540A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="kinematicEval" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="37">
   <si>
     <t>tx</t>
   </si>
@@ -134,13 +134,19 @@
   <si>
     <t>Significance RMSE</t>
   </si>
+  <si>
+    <t>n=3</t>
+  </si>
+  <si>
+    <t>DoF</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -186,7 +192,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -291,88 +297,241 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="148">
+  <dxfs count="35">
     <dxf>
       <font>
-        <color rgb="FF00B050"/>
+        <b/>
+        <i val="0"/>
       </font>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -390,60 +549,6 @@
       <font>
         <color rgb="FFC00000"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFCCCC"/>
@@ -522,56 +627,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF00B050"/>
       </font>
       <fill>
@@ -593,46 +648,6 @@
     <dxf>
       <font>
         <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
       </font>
       <fill>
         <patternFill>
@@ -672,86 +687,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -777,207 +712,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1103,494 +837,6 @@
         <b/>
         <i val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
@@ -1919,41 +1165,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="5" t="s">
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5" t="s">
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -2453,31 +1699,31 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="5" t="s">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5" t="s">
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -2928,22 +2174,22 @@
       <c r="P18" s="2"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="9" t="s">
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="9" t="s">
+      <c r="F19" s="27"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="10"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
@@ -2952,32 +2198,32 @@
       <c r="P19" s="2"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="25" t="s">
         <v>13</v>
       </c>
       <c r="K20" s="2"/>
@@ -2988,42 +2234,42 @@
       <c r="P20" s="2"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="8">
         <f>B3</f>
         <v>3.69514731172226</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="5">
         <f>G3</f>
         <v>6.70967570784362</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="9">
         <f>L3</f>
         <v>5.5308895664222497</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="8">
         <f>D3</f>
         <v>3.3686852316004501</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="5">
         <f>I3</f>
         <v>2.6610672031828502</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="9">
         <f>N3</f>
         <v>2.95538725349817</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="8">
         <f>F3</f>
         <v>0.99600004112783203</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="5">
         <f>K3</f>
         <v>0.98133763413798303</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="9">
         <f>P3</f>
         <v>0.99055095826475403</v>
       </c>
@@ -3035,42 +2281,42 @@
       <c r="P21" s="2"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="8">
         <f t="shared" ref="B22:B26" si="15">B4</f>
         <v>2.2970250944358401</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="5">
         <f t="shared" ref="C22:C26" si="16">G4</f>
         <v>7.1672808940967396</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="9">
         <f t="shared" ref="D22:D26" si="17">L4</f>
         <v>6.7613878415646802</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="8">
         <f t="shared" ref="E22:E26" si="18">D4</f>
         <v>1.4261592430915999</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="5">
         <f t="shared" ref="F22:F26" si="19">I4</f>
         <v>6.6804859675955601</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="9">
         <f t="shared" ref="G22:G26" si="20">N4</f>
         <v>6.4965713099578997</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="8">
         <f t="shared" ref="H22:H26" si="21">F4</f>
         <v>0.92308484798192603</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="5">
         <f t="shared" ref="I22:I26" si="22">K4</f>
         <v>0.626160533408048</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="9">
         <f t="shared" ref="J22:J26" si="23">P4</f>
         <v>0.68318914881161197</v>
       </c>
@@ -3082,42 +2328,42 @@
       <c r="P22" s="2"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="8">
         <f t="shared" si="15"/>
         <v>0.99948141482634101</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="5">
         <f t="shared" si="16"/>
         <v>2.4235663623461101</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="9">
         <f t="shared" si="17"/>
         <v>3.4127441136584702</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="8">
         <f t="shared" si="18"/>
         <v>0.67899885034825203</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="5">
         <f t="shared" si="19"/>
         <v>2.3070522111021798</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="9">
         <f t="shared" si="20"/>
         <v>3.1472185029143498</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="8">
         <f t="shared" si="21"/>
         <v>0.74302324011302501</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="5">
         <f t="shared" si="22"/>
         <v>0.49611207988471301</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="9">
         <f t="shared" si="23"/>
         <v>0.29808218227862499</v>
       </c>
@@ -3129,42 +2375,42 @@
       <c r="P23" s="2"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="8">
         <f t="shared" si="15"/>
         <v>0.717275929128246</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="5">
         <f t="shared" si="16"/>
         <v>1.2160825814348699</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="9">
         <f t="shared" si="17"/>
         <v>1.9229685932921201</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="8">
         <f t="shared" si="18"/>
         <v>0.65739546433538998</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="5">
         <f t="shared" si="19"/>
         <v>1.2096420132655501</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="9">
         <f t="shared" si="20"/>
         <v>1.9293844477486199</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="8">
         <f t="shared" si="21"/>
         <v>0.97304979668886304</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="5">
         <f t="shared" si="22"/>
         <v>0.99508197809270205</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="9">
         <f t="shared" si="23"/>
         <v>0.99224936689461696</v>
       </c>
@@ -3176,42 +2422,42 @@
       <c r="P24" s="2"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="8">
         <f t="shared" si="15"/>
         <v>4.5775773225284704</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="5">
         <f t="shared" si="16"/>
         <v>17.4434409638693</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="9">
         <f t="shared" si="17"/>
         <v>15.5616090803326</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="8">
         <f t="shared" si="18"/>
         <v>4.0918969835559498</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="5">
         <f t="shared" si="19"/>
         <v>18.587816726253401</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="9">
         <f t="shared" si="20"/>
         <v>16.165644091576201</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="8">
         <f t="shared" si="21"/>
         <v>0.79890660118759105</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="5">
         <f t="shared" si="22"/>
         <v>0.71862490300105397</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="9">
         <f t="shared" si="23"/>
         <v>0.74340218007859604</v>
       </c>
@@ -3223,42 +2469,42 @@
       <c r="P25" s="2"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="8">
         <f t="shared" si="15"/>
         <v>0.50900771582851201</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="5">
         <f t="shared" si="16"/>
         <v>2.6122458015866998</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="9">
         <f t="shared" si="17"/>
         <v>3.1026851952282901</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="8">
         <f t="shared" si="18"/>
         <v>0.32779202230136001</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="5">
         <f t="shared" si="19"/>
         <v>2.5290153348047002</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="9">
         <f t="shared" si="20"/>
         <v>3.1870257516359199</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="8">
         <f t="shared" si="21"/>
         <v>0.99984459783193003</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="5">
         <f t="shared" si="22"/>
         <v>0.99842303013932698</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="9">
         <f t="shared" si="23"/>
         <v>0.99924920096632697</v>
       </c>
@@ -3270,304 +2516,307 @@
       <c r="P26" s="2"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="16" t="s">
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="16" t="s">
+      <c r="F28" s="30"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="18"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="31"/>
       <c r="L28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="11" t="s">
+    <row r="29" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="43"/>
+      <c r="B29" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="41" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="19" t="str">
+      <c r="B30" s="33" t="str">
         <f>B12</f>
         <v>3.70 ± 1.06</v>
       </c>
-      <c r="C30" s="8" t="str">
+      <c r="C30" s="34" t="str">
         <f>E12</f>
         <v>6.71 ± 5.13</v>
       </c>
-      <c r="D30" s="14" t="str">
+      <c r="D30" s="35" t="str">
         <f>H12</f>
         <v>5.53 ± 3.92</v>
       </c>
-      <c r="E30" s="27" t="str">
+      <c r="E30" s="36" t="str">
         <f>C12</f>
         <v>3.37 ▴ 6.79</v>
       </c>
-      <c r="F30" s="28" t="str">
+      <c r="F30" s="37" t="str">
         <f>F12</f>
         <v>2.66 ▴ 17.08</v>
       </c>
-      <c r="G30" s="12" t="str">
+      <c r="G30" s="38" t="str">
         <f>I12</f>
         <v>2.96 ▴ 13.05</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="33">
         <f>D12</f>
         <v>0.99600004112783203</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="34">
         <f>G12</f>
         <v>0.98133763413798303</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="35">
         <f>J12</f>
         <v>0.99055095826475403</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="19" t="str">
+      <c r="B31" s="11" t="str">
         <f t="shared" ref="B31:B35" si="24">B13</f>
         <v>2.30 ± 1.60</v>
       </c>
-      <c r="C31" s="8" t="str">
+      <c r="C31" s="5" t="str">
         <f t="shared" ref="C31:C35" si="25">E13</f>
         <v>7.17 ± 1.77</v>
       </c>
-      <c r="D31" s="14" t="str">
+      <c r="D31" s="9" t="str">
         <f t="shared" ref="D31:D35" si="26">H13</f>
         <v>6.76 ± 1.85</v>
       </c>
-      <c r="E31" s="21" t="str">
+      <c r="E31" s="13" t="str">
         <f t="shared" ref="E31:E35" si="27">C13</f>
         <v>1.43 ▴ 4.80</v>
       </c>
-      <c r="F31" s="6" t="str">
+      <c r="F31" s="4" t="str">
         <f t="shared" ref="F31:F35" si="28">F13</f>
         <v>6.68 ▴ 10.75</v>
       </c>
-      <c r="G31" s="12" t="str">
+      <c r="G31" s="7" t="str">
         <f t="shared" ref="G31:G35" si="29">I13</f>
         <v>6.50 ▴ 11.38</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="11">
         <f t="shared" ref="H31:H35" si="30">D13</f>
         <v>0.92308484798192603</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="5">
         <f t="shared" ref="I31:I35" si="31">G13</f>
         <v>0.626160533408048</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="9">
         <f t="shared" ref="J31:J35" si="32">J13</f>
         <v>0.68318914881161197</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="19" t="str">
+      <c r="B32" s="11" t="str">
         <f t="shared" si="24"/>
         <v>1.00 ± 0.97</v>
       </c>
-      <c r="C32" s="8" t="str">
+      <c r="C32" s="5" t="str">
         <f t="shared" si="25"/>
         <v>2.42 ± 1.18</v>
       </c>
-      <c r="D32" s="14" t="str">
+      <c r="D32" s="9" t="str">
         <f t="shared" si="26"/>
         <v>3.41 ± 1.43</v>
       </c>
-      <c r="E32" s="21" t="str">
+      <c r="E32" s="13" t="str">
         <f t="shared" si="27"/>
         <v>0.68 ▴ 2.28</v>
       </c>
-      <c r="F32" s="6" t="str">
+      <c r="F32" s="4" t="str">
         <f t="shared" si="28"/>
         <v>2.31 ▴ 4.43</v>
       </c>
-      <c r="G32" s="12" t="str">
+      <c r="G32" s="7" t="str">
         <f t="shared" si="29"/>
         <v>3.15 ▴ 6.04</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="11">
         <f t="shared" si="30"/>
         <v>0.74302324011302501</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <f t="shared" si="31"/>
         <v>0.49611207988471301</v>
       </c>
-      <c r="J32" s="14">
+      <c r="J32" s="9">
         <f t="shared" si="32"/>
         <v>0.29808218227862499</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="19" t="str">
+      <c r="B33" s="11" t="str">
         <f t="shared" si="24"/>
         <v>0.72 ± 0.35</v>
       </c>
-      <c r="C33" s="8" t="str">
+      <c r="C33" s="5" t="str">
         <f t="shared" si="25"/>
         <v>1.22 ± 0.29</v>
       </c>
-      <c r="D33" s="14" t="str">
+      <c r="D33" s="9" t="str">
         <f t="shared" si="26"/>
         <v>1.92 ± 0.33</v>
       </c>
-      <c r="E33" s="21" t="str">
+      <c r="E33" s="13" t="str">
         <f t="shared" si="27"/>
         <v>0.66 ▴ 1.35</v>
       </c>
-      <c r="F33" s="6" t="str">
+      <c r="F33" s="4" t="str">
         <f t="shared" si="28"/>
         <v>1.21 ▴ 1.79</v>
       </c>
-      <c r="G33" s="12" t="str">
+      <c r="G33" s="7" t="str">
         <f t="shared" si="29"/>
         <v>1.93 ▴ 2.58</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="8">
         <f t="shared" si="30"/>
         <v>0.97304979668886304</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="14">
         <f t="shared" si="31"/>
         <v>0.99508197809270205</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="9">
         <f t="shared" si="32"/>
         <v>0.99224936689461696</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="19" t="str">
+      <c r="B34" s="11" t="str">
         <f t="shared" si="24"/>
         <v>4.58 ± 2.52</v>
       </c>
-      <c r="C34" s="8" t="str">
+      <c r="C34" s="5" t="str">
         <f t="shared" si="25"/>
         <v>17.44 ± 8.80</v>
       </c>
-      <c r="D34" s="14" t="str">
+      <c r="D34" s="9" t="str">
         <f t="shared" si="26"/>
         <v>15.56 ± 5.46</v>
       </c>
-      <c r="E34" s="21" t="str">
+      <c r="E34" s="13" t="str">
         <f t="shared" si="27"/>
         <v>4.09 ▴ 10.24</v>
       </c>
-      <c r="F34" s="6" t="str">
+      <c r="F34" s="4" t="str">
         <f t="shared" si="28"/>
         <v>18.59 ▴ 27.57</v>
       </c>
-      <c r="G34" s="12" t="str">
+      <c r="G34" s="7" t="str">
         <f t="shared" si="29"/>
         <v>16.17 ▴ 22.33</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="11">
         <f t="shared" si="30"/>
         <v>0.79890660118759105</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="5">
         <f t="shared" si="31"/>
         <v>0.71862490300105397</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="9">
         <f t="shared" si="32"/>
         <v>0.74340218007859604</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="19" t="str">
+      <c r="B35" s="11" t="str">
         <f t="shared" si="24"/>
         <v>0.51 ± 0.49</v>
       </c>
-      <c r="C35" s="8" t="str">
+      <c r="C35" s="5" t="str">
         <f t="shared" si="25"/>
         <v>2.61 ± 1.35</v>
       </c>
-      <c r="D35" s="14" t="str">
+      <c r="D35" s="9" t="str">
         <f t="shared" si="26"/>
         <v>3.10 ± 0.90</v>
       </c>
-      <c r="E35" s="21" t="str">
+      <c r="E35" s="13" t="str">
         <f t="shared" si="27"/>
         <v>0.33 ▴ 1.26</v>
       </c>
-      <c r="F35" s="6" t="str">
+      <c r="F35" s="4" t="str">
         <f t="shared" si="28"/>
         <v>2.53 ▴ 5.39</v>
       </c>
-      <c r="G35" s="12" t="str">
+      <c r="G35" s="7" t="str">
         <f t="shared" si="29"/>
         <v>3.19 ▴ 5.05</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="11">
         <f t="shared" si="30"/>
         <v>0.99984459783193003</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="5">
         <f t="shared" si="31"/>
         <v>0.99842303013932698</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="9">
         <f t="shared" si="32"/>
         <v>0.99924920096632697</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="H28:J28"/>
@@ -3586,23 +2835,23 @@
     <mergeCell ref="V1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="B21:D26">
-    <cfRule type="expression" dxfId="82" priority="4">
+    <cfRule type="expression" dxfId="34" priority="4">
       <formula>B21=MIN($B21:$D21)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B30:D35">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>B30=MIN($B30:$D30)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E21:G26">
-    <cfRule type="expression" dxfId="81" priority="3">
+    <cfRule type="expression" dxfId="32" priority="3">
       <formula>E21=MIN($E21:$G21)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:J26">
-    <cfRule type="expression" dxfId="80" priority="2">
+    <cfRule type="expression" dxfId="31" priority="2">
       <formula>H21=MAX($H21:$J21)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30:D35">
-    <cfRule type="expression" dxfId="79" priority="1">
-      <formula>B30=MIN($B30:$D30)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3623,27 +2872,27 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -3998,27 +3247,27 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -4368,31 +3617,31 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="17"/>
+      <c r="D21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4" t="s">
+      <c r="E21" s="17"/>
+      <c r="F21" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="9" t="s">
+      <c r="G21" s="17"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="9" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="9" t="s">
+      <c r="M21" s="20"/>
+      <c r="N21" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="O21" s="10"/>
+      <c r="O21" s="20"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
@@ -4413,23 +3662,23 @@
       <c r="G22" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="11" t="s">
+      <c r="I22" s="10"/>
+      <c r="J22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="N22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O22" s="12" t="s">
+      <c r="O22" s="7" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4461,31 +3710,31 @@
         <f>L14</f>
         <v>6.0778871222411297</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="J23" s="11" t="str">
-        <f>TEXT(B4,"0.00") &amp; " ± " &amp; TEXT(C4,"0.00")</f>
+      <c r="J23" s="6" t="str">
+        <f t="shared" ref="J23:J28" si="0">TEXT(B4,"0.00") &amp; " ± " &amp; TEXT(C4,"0.00")</f>
         <v>3.21 ± 0.91</v>
       </c>
-      <c r="K23" s="12" t="str">
-        <f>TEXT(B14,"0.00") &amp; " ± " &amp; TEXT(C14,"0.00")</f>
+      <c r="K23" s="7" t="str">
+        <f t="shared" ref="K23:K28" si="1">TEXT(B14,"0.00") &amp; " ± " &amp; TEXT(C14,"0.00")</f>
         <v>4.09 ± 1.13</v>
       </c>
-      <c r="L23" s="11" t="str">
-        <f>TEXT(G4,"0.00") &amp; " ± " &amp; TEXT(H4,"0.00")</f>
+      <c r="L23" s="6" t="str">
+        <f t="shared" ref="L23:L28" si="2">TEXT(G4,"0.00") &amp; " ± " &amp; TEXT(H4,"0.00")</f>
         <v>6.65 ± 5.24</v>
       </c>
-      <c r="M23" s="12" t="str">
-        <f>TEXT(G14,"0.00") &amp; " ± " &amp; TEXT(H14,"0.00")</f>
+      <c r="M23" s="7" t="str">
+        <f t="shared" ref="M23:M28" si="3">TEXT(G14,"0.00") &amp; " ± " &amp; TEXT(H14,"0.00")</f>
         <v>6.07 ± 4.61</v>
       </c>
-      <c r="N23" s="11" t="str">
-        <f>TEXT(L4,"0.00") &amp; " ± " &amp; TEXT(M4,"0.00")</f>
+      <c r="N23" s="6" t="str">
+        <f t="shared" ref="N23:N28" si="4">TEXT(L4,"0.00") &amp; " ± " &amp; TEXT(M4,"0.00")</f>
         <v>5.29 ± 3.85</v>
       </c>
-      <c r="O23" s="12" t="str">
-        <f>TEXT(L14,"0.00") &amp; " ± " &amp; TEXT(M14,"0.00")</f>
+      <c r="O23" s="7" t="str">
+        <f t="shared" ref="O23:O28" si="5">TEXT(L14,"0.00") &amp; " ± " &amp; TEXT(M14,"0.00")</f>
         <v>6.08 ± 4.22</v>
       </c>
     </row>
@@ -4494,54 +3743,54 @@
         <v>1</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" ref="B24:B28" si="0">B5</f>
+        <f t="shared" ref="B24:B28" si="6">B5</f>
         <v>1.8272305635616399</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" ref="C24:C28" si="1">B15</f>
+        <f t="shared" ref="C24:C28" si="7">B15</f>
         <v>2.26330540363143</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" ref="D24:D28" si="2">G5</f>
+        <f t="shared" ref="D24:D28" si="8">G5</f>
         <v>7.0639384798379998</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" ref="E24:E28" si="3">G15</f>
+        <f t="shared" ref="E24:E28" si="9">G15</f>
         <v>6.5630790613226404</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" ref="F24:F28" si="4">L5</f>
+        <f t="shared" ref="F24:F28" si="10">L5</f>
         <v>6.1217279888108704</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" ref="G24:G28" si="5">L15</f>
+        <f t="shared" ref="G24:G28" si="11">L15</f>
         <v>7.0066382566082597</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="J24" s="11" t="str">
-        <f>TEXT(B5,"0.00") &amp; " ± " &amp; TEXT(C5,"0.00")</f>
+      <c r="J24" s="6" t="str">
+        <f t="shared" si="0"/>
         <v>1.83 ± 1.26</v>
       </c>
-      <c r="K24" s="12" t="str">
-        <f>TEXT(B15,"0.00") &amp; " ± " &amp; TEXT(C15,"0.00")</f>
+      <c r="K24" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>2.26 ± 1.30</v>
       </c>
-      <c r="L24" s="11" t="str">
-        <f>TEXT(G5,"0.00") &amp; " ± " &amp; TEXT(H5,"0.00")</f>
+      <c r="L24" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>7.06 ± 1.36</v>
       </c>
-      <c r="M24" s="12" t="str">
-        <f>TEXT(G15,"0.00") &amp; " ± " &amp; TEXT(H15,"0.00")</f>
+      <c r="M24" s="7" t="str">
+        <f t="shared" si="3"/>
         <v>6.56 ± 1.55</v>
       </c>
-      <c r="N24" s="11" t="str">
-        <f>TEXT(L5,"0.00") &amp; " ± " &amp; TEXT(M5,"0.00")</f>
+      <c r="N24" s="6" t="str">
+        <f t="shared" si="4"/>
         <v>6.12 ± 1.70</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <f>TEXT(L15,"0.00") &amp; " ± " &amp; TEXT(M15,"0.00")</f>
+      <c r="O24" s="7" t="str">
+        <f t="shared" si="5"/>
         <v>7.01 ± 1.69</v>
       </c>
     </row>
@@ -4550,54 +3799,54 @@
         <v>2</v>
       </c>
       <c r="B25" s="1">
+        <f t="shared" si="6"/>
+        <v>1.2815784691674601</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="7"/>
+        <v>0.76123516349491305</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="8"/>
+        <v>2.44907060232415</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="9"/>
+        <v>2.2515928648182499</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="10"/>
+        <v>3.85652302359202</v>
+      </c>
+      <c r="G25" s="1">
+        <f t="shared" si="11"/>
+        <v>2.7142584235473102</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>1.2815784691674601</v>
-      </c>
-      <c r="C25" s="1">
+        <v>1.28 ± 0.88</v>
+      </c>
+      <c r="K25" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0.76123516349491305</v>
-      </c>
-      <c r="D25" s="1">
+        <v>0.76 ± 0.74</v>
+      </c>
+      <c r="L25" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>2.44907060232415</v>
-      </c>
-      <c r="E25" s="1">
+        <v>2.45 ± 1.11</v>
+      </c>
+      <c r="M25" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>2.2515928648182499</v>
-      </c>
-      <c r="F25" s="1">
+        <v>2.25 ± 1.27</v>
+      </c>
+      <c r="N25" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3.85652302359202</v>
-      </c>
-      <c r="G25" s="1">
+        <v>3.86 ± 1.36</v>
+      </c>
+      <c r="O25" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>2.7142584235473102</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="J25" s="11" t="str">
-        <f>TEXT(B6,"0.00") &amp; " ± " &amp; TEXT(C6,"0.00")</f>
-        <v>1.28 ± 0.88</v>
-      </c>
-      <c r="K25" s="12" t="str">
-        <f>TEXT(B16,"0.00") &amp; " ± " &amp; TEXT(C16,"0.00")</f>
-        <v>0.76 ± 0.74</v>
-      </c>
-      <c r="L25" s="11" t="str">
-        <f>TEXT(G6,"0.00") &amp; " ± " &amp; TEXT(H6,"0.00")</f>
-        <v>2.45 ± 1.11</v>
-      </c>
-      <c r="M25" s="12" t="str">
-        <f>TEXT(G16,"0.00") &amp; " ± " &amp; TEXT(H16,"0.00")</f>
-        <v>2.25 ± 1.27</v>
-      </c>
-      <c r="N25" s="11" t="str">
-        <f>TEXT(L6,"0.00") &amp; " ± " &amp; TEXT(M6,"0.00")</f>
-        <v>3.86 ± 1.36</v>
-      </c>
-      <c r="O25" s="12" t="str">
-        <f>TEXT(L16,"0.00") &amp; " ± " &amp; TEXT(M16,"0.00")</f>
         <v>2.71 ± 1.24</v>
       </c>
     </row>
@@ -4606,54 +3855,54 @@
         <v>3</v>
       </c>
       <c r="B26" s="1">
+        <f t="shared" si="6"/>
+        <v>0.41377717832845101</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="7"/>
+        <v>0.85379028385400701</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="8"/>
+        <v>1.2215939217885099</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="9"/>
+        <v>1.16157293661143</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="10"/>
+        <v>1.9989106633526399</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="11"/>
+        <v>1.8021812002780599</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.41377717832845101</v>
-      </c>
-      <c r="C26" s="1">
+        <v>0.41 ± 0.27</v>
+      </c>
+      <c r="K26" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0.85379028385400701</v>
-      </c>
-      <c r="D26" s="1">
+        <v>0.85 ± 0.23</v>
+      </c>
+      <c r="L26" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>1.2215939217885099</v>
-      </c>
-      <c r="E26" s="1">
+        <v>1.22 ± 0.28</v>
+      </c>
+      <c r="M26" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.16157293661143</v>
-      </c>
-      <c r="F26" s="1">
+        <v>1.16 ± 0.31</v>
+      </c>
+      <c r="N26" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>1.9989106633526399</v>
-      </c>
-      <c r="G26" s="1">
+        <v>2.00 ± 0.33</v>
+      </c>
+      <c r="O26" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1.8021812002780599</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="11" t="str">
-        <f>TEXT(B7,"0.00") &amp; " ± " &amp; TEXT(C7,"0.00")</f>
-        <v>0.41 ± 0.27</v>
-      </c>
-      <c r="K26" s="12" t="str">
-        <f>TEXT(B17,"0.00") &amp; " ± " &amp; TEXT(C17,"0.00")</f>
-        <v>0.85 ± 0.23</v>
-      </c>
-      <c r="L26" s="11" t="str">
-        <f>TEXT(G7,"0.00") &amp; " ± " &amp; TEXT(H7,"0.00")</f>
-        <v>1.22 ± 0.28</v>
-      </c>
-      <c r="M26" s="12" t="str">
-        <f>TEXT(G17,"0.00") &amp; " ± " &amp; TEXT(H17,"0.00")</f>
-        <v>1.16 ± 0.31</v>
-      </c>
-      <c r="N26" s="11" t="str">
-        <f>TEXT(L7,"0.00") &amp; " ± " &amp; TEXT(M7,"0.00")</f>
-        <v>2.00 ± 0.33</v>
-      </c>
-      <c r="O26" s="12" t="str">
-        <f>TEXT(L17,"0.00") &amp; " ± " &amp; TEXT(M17,"0.00")</f>
         <v>1.80 ± 0.33</v>
       </c>
     </row>
@@ -4662,54 +3911,54 @@
         <v>4</v>
       </c>
       <c r="B27" s="1">
+        <f t="shared" si="6"/>
+        <v>5.4646244811304303</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="7"/>
+        <v>4.2955416675485303</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="8"/>
+        <v>17.547896274193899</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="9"/>
+        <v>18.099372618286001</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="10"/>
+        <v>15.8315786186881</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="11"/>
+        <v>15.737257194167499</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>5.4646244811304303</v>
-      </c>
-      <c r="C27" s="1">
+        <v>5.46 ± 2.30</v>
+      </c>
+      <c r="K27" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>4.2955416675485303</v>
-      </c>
-      <c r="D27" s="1">
+        <v>4.30 ± 2.13</v>
+      </c>
+      <c r="L27" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>17.547896274193899</v>
-      </c>
-      <c r="E27" s="1">
+        <v>17.55 ± 7.86</v>
+      </c>
+      <c r="M27" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>18.099372618286001</v>
-      </c>
-      <c r="F27" s="1">
+        <v>18.10 ± 7.25</v>
+      </c>
+      <c r="N27" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>15.8315786186881</v>
-      </c>
-      <c r="G27" s="1">
+        <v>15.83 ± 4.42</v>
+      </c>
+      <c r="O27" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>15.737257194167499</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="11" t="str">
-        <f>TEXT(B8,"0.00") &amp; " ± " &amp; TEXT(C8,"0.00")</f>
-        <v>5.46 ± 2.30</v>
-      </c>
-      <c r="K27" s="12" t="str">
-        <f>TEXT(B18,"0.00") &amp; " ± " &amp; TEXT(C18,"0.00")</f>
-        <v>4.30 ± 2.13</v>
-      </c>
-      <c r="L27" s="11" t="str">
-        <f>TEXT(G8,"0.00") &amp; " ± " &amp; TEXT(H8,"0.00")</f>
-        <v>17.55 ± 7.86</v>
-      </c>
-      <c r="M27" s="12" t="str">
-        <f>TEXT(G18,"0.00") &amp; " ± " &amp; TEXT(H18,"0.00")</f>
-        <v>18.10 ± 7.25</v>
-      </c>
-      <c r="N27" s="11" t="str">
-        <f>TEXT(L8,"0.00") &amp; " ± " &amp; TEXT(M8,"0.00")</f>
-        <v>15.83 ± 4.42</v>
-      </c>
-      <c r="O27" s="12" t="str">
-        <f>TEXT(L18,"0.00") &amp; " ± " &amp; TEXT(M18,"0.00")</f>
         <v>15.74 ± 5.50</v>
       </c>
     </row>
@@ -4718,83 +3967,83 @@
         <v>5</v>
       </c>
       <c r="B28" s="1">
+        <f t="shared" si="6"/>
+        <v>0.45960260884256998</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="7"/>
+        <v>0.49745826098954499</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="8"/>
+        <v>2.6670859091564001</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="9"/>
+        <v>2.71459140188264</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="10"/>
+        <v>3.1487293164673198</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="11"/>
+        <v>3.13020600521227</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J28" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.45960260884256998</v>
-      </c>
-      <c r="C28" s="1">
+        <v>0.46 ± 0.46</v>
+      </c>
+      <c r="K28" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0.49745826098954499</v>
-      </c>
-      <c r="D28" s="1">
+        <v>0.50 ± 0.49</v>
+      </c>
+      <c r="L28" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>2.6670859091564001</v>
-      </c>
-      <c r="E28" s="1">
+        <v>2.67 ± 1.22</v>
+      </c>
+      <c r="M28" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>2.71459140188264</v>
-      </c>
-      <c r="F28" s="1">
+        <v>2.71 ± 1.17</v>
+      </c>
+      <c r="N28" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3.1487293164673198</v>
-      </c>
-      <c r="G28" s="1">
+        <v>3.15 ± 0.66</v>
+      </c>
+      <c r="O28" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>3.13020600521227</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J28" s="11" t="str">
-        <f>TEXT(B9,"0.00") &amp; " ± " &amp; TEXT(C9,"0.00")</f>
-        <v>0.46 ± 0.46</v>
-      </c>
-      <c r="K28" s="12" t="str">
-        <f>TEXT(B19,"0.00") &amp; " ± " &amp; TEXT(C19,"0.00")</f>
-        <v>0.50 ± 0.49</v>
-      </c>
-      <c r="L28" s="11" t="str">
-        <f>TEXT(G9,"0.00") &amp; " ± " &amp; TEXT(H9,"0.00")</f>
-        <v>2.67 ± 1.22</v>
-      </c>
-      <c r="M28" s="12" t="str">
-        <f>TEXT(G19,"0.00") &amp; " ± " &amp; TEXT(H19,"0.00")</f>
-        <v>2.71 ± 1.17</v>
-      </c>
-      <c r="N28" s="11" t="str">
-        <f>TEXT(L9,"0.00") &amp; " ± " &amp; TEXT(M9,"0.00")</f>
-        <v>3.15 ± 0.66</v>
-      </c>
-      <c r="O28" s="12" t="str">
-        <f>TEXT(L19,"0.00") &amp; " ± " &amp; TEXT(M19,"0.00")</f>
         <v>3.13 ± 1.01</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4" t="s">
+      <c r="C30" s="17"/>
+      <c r="D30" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4" t="s">
+      <c r="E30" s="17"/>
+      <c r="F30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="9" t="s">
+      <c r="G30" s="17"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="9" t="s">
+      <c r="K30" s="20"/>
+      <c r="L30" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M30" s="10"/>
-      <c r="N30" s="9" t="s">
+      <c r="M30" s="20"/>
+      <c r="N30" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="O30" s="10"/>
+      <c r="O30" s="20"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
@@ -4815,23 +4064,23 @@
       <c r="G31" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15"/>
-      <c r="J31" s="11" t="s">
+      <c r="I31" s="10"/>
+      <c r="J31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M31" s="12" t="s">
+      <c r="M31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N31" s="11" t="s">
+      <c r="N31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O31" s="12" t="s">
+      <c r="O31" s="7" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4863,31 +4112,31 @@
         <f>N14</f>
         <v>3.6630578537298102</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="J32" s="11" t="str">
-        <f>TEXT(D4,"0.00") &amp; " ▴ " &amp; TEXT(E4,"0.00")</f>
+      <c r="J32" s="6" t="str">
+        <f t="shared" ref="J32:J37" si="12">TEXT(D4,"0.00") &amp; " ▴ " &amp; TEXT(E4,"0.00")</f>
         <v>2.87 ▴ 5.27</v>
       </c>
-      <c r="K32" s="12" t="str">
-        <f>TEXT(D14,"0.00") &amp; " ▴ " &amp; TEXT(E14,"0.00")</f>
+      <c r="K32" s="7" t="str">
+        <f t="shared" ref="K32:K37" si="13">TEXT(D14,"0.00") &amp; " ▴ " &amp; TEXT(E14,"0.00")</f>
         <v>3.87 ▴ 6.81</v>
       </c>
-      <c r="L32" s="11" t="str">
-        <f>TEXT(I4,"0.00") &amp; " ▴ " &amp; TEXT(J4,"0.00")</f>
+      <c r="L32" s="6" t="str">
+        <f t="shared" ref="L32:L37" si="14">TEXT(I4,"0.00") &amp; " ▴ " &amp; TEXT(J4,"0.00")</f>
         <v>1.67 ▴ 17.07</v>
       </c>
-      <c r="M32" s="12" t="str">
-        <f>TEXT(I14,"0.00") &amp; " ▴ " &amp; TEXT(J14,"0.00")</f>
+      <c r="M32" s="7" t="str">
+        <f t="shared" ref="M32:M37" si="15">TEXT(I14,"0.00") &amp; " ▴ " &amp; TEXT(J14,"0.00")</f>
         <v>2.86 ▴ 14.53</v>
       </c>
-      <c r="N32" s="11" t="str">
-        <f>TEXT(N4,"0.00") &amp; " ▴ " &amp; TEXT(O4,"0.00")</f>
+      <c r="N32" s="6" t="str">
+        <f t="shared" ref="N32:N37" si="16">TEXT(N4,"0.00") &amp; " ▴ " &amp; TEXT(O4,"0.00")</f>
         <v>2.39 ▴ 13.05</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <f>TEXT(N14,"0.00") &amp; " ▴ " &amp; TEXT(O14,"0.00")</f>
+      <c r="O32" s="7" t="str">
+        <f t="shared" ref="O32:O37" si="17">TEXT(N14,"0.00") &amp; " ▴ " &amp; TEXT(O14,"0.00")</f>
         <v>3.66 ▴ 11.92</v>
       </c>
     </row>
@@ -4896,54 +4145,54 @@
         <v>1</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" ref="B33:B37" si="6">D5</f>
+        <f t="shared" ref="B33:B37" si="18">D5</f>
         <v>1.3433967767398101</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" ref="C33:C37" si="7">D15</f>
+        <f t="shared" ref="C33:C37" si="19">D15</f>
         <v>1.7267247613207899</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" ref="D33:D37" si="8">I5</f>
+        <f t="shared" ref="D33:D37" si="20">I5</f>
         <v>6.7091501687396597</v>
       </c>
       <c r="E33" s="1">
-        <f t="shared" ref="E33:E37" si="9">I15</f>
+        <f t="shared" ref="E33:E37" si="21">I15</f>
         <v>6.5875819010309602</v>
       </c>
       <c r="F33" s="1">
-        <f t="shared" ref="F33:F37" si="10">N5</f>
+        <f t="shared" ref="F33:F37" si="22">N5</f>
         <v>6.0693888007527299</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" ref="G33:G37" si="11">N15</f>
+        <f t="shared" ref="G33:G37" si="23">N15</f>
         <v>6.6377020590646802</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="J33" s="11" t="str">
-        <f>TEXT(D5,"0.00") &amp; " ▴ " &amp; TEXT(E5,"0.00")</f>
+      <c r="J33" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>1.34 ▴ 4.06</v>
       </c>
-      <c r="K33" s="12" t="str">
-        <f>TEXT(D15,"0.00") &amp; " ▴ " &amp; TEXT(E15,"0.00")</f>
+      <c r="K33" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>1.73 ▴ 4.37</v>
       </c>
-      <c r="L33" s="11" t="str">
-        <f>TEXT(I5,"0.00") &amp; " ▴ " &amp; TEXT(J5,"0.00")</f>
+      <c r="L33" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>6.71 ▴ 10.04</v>
       </c>
-      <c r="M33" s="12" t="str">
-        <f>TEXT(I15,"0.00") &amp; " ▴ " &amp; TEXT(J15,"0.00")</f>
+      <c r="M33" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>6.59 ▴ 9.02</v>
       </c>
-      <c r="N33" s="11" t="str">
-        <f>TEXT(N5,"0.00") &amp; " ▴ " &amp; TEXT(O5,"0.00")</f>
+      <c r="N33" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>6.07 ▴ 10.15</v>
       </c>
-      <c r="O33" s="12" t="str">
-        <f>TEXT(N15,"0.00") &amp; " ▴ " &amp; TEXT(O15,"0.00")</f>
+      <c r="O33" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>6.64 ▴ 11.06</v>
       </c>
     </row>
@@ -4952,54 +4201,54 @@
         <v>2</v>
       </c>
       <c r="B34" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>1.00507089517066</v>
       </c>
       <c r="C34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>0.53522748019432598</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>2.2640863509146101</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>2.1095362189402298</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>3.4661718529955499</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>2.6486084869154398</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="J34" s="11" t="str">
-        <f>TEXT(D6,"0.00") &amp; " ▴ " &amp; TEXT(E6,"0.00")</f>
+      <c r="J34" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>1.01 ▴ 3.11</v>
       </c>
-      <c r="K34" s="12" t="str">
-        <f>TEXT(D16,"0.00") &amp; " ▴ " &amp; TEXT(E16,"0.00")</f>
+      <c r="K34" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>0.54 ▴ 1.61</v>
       </c>
-      <c r="L34" s="11" t="str">
-        <f>TEXT(I6,"0.00") &amp; " ▴ " &amp; TEXT(J6,"0.00")</f>
+      <c r="L34" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>2.26 ▴ 4.43</v>
       </c>
-      <c r="M34" s="12" t="str">
-        <f>TEXT(I16,"0.00") &amp; " ▴ " &amp; TEXT(J16,"0.00")</f>
+      <c r="M34" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>2.11 ▴ 4.01</v>
       </c>
-      <c r="N34" s="11" t="str">
-        <f>TEXT(N6,"0.00") &amp; " ▴ " &amp; TEXT(O6,"0.00")</f>
+      <c r="N34" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>3.47 ▴ 6.04</v>
       </c>
-      <c r="O34" s="12" t="str">
-        <f>TEXT(N16,"0.00") &amp; " ▴ " &amp; TEXT(O16,"0.00")</f>
+      <c r="O34" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>2.65 ▴ 4.65</v>
       </c>
     </row>
@@ -5008,54 +4257,54 @@
         <v>3</v>
       </c>
       <c r="B35" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>0.27054172691310202</v>
       </c>
       <c r="C35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>0.84387955346518195</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>1.19193064784142</v>
       </c>
       <c r="E35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>1.1827980487996701</v>
       </c>
       <c r="F35" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>1.9932274136964001</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>1.8032077594970399</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J35" s="11" t="str">
-        <f>TEXT(D7,"0.00") &amp; " ▴ " &amp; TEXT(E7,"0.00")</f>
+      <c r="J35" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>0.27 ▴ 0.93</v>
       </c>
-      <c r="K35" s="12" t="str">
-        <f>TEXT(D17,"0.00") &amp; " ▴ " &amp; TEXT(E17,"0.00")</f>
+      <c r="K35" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>0.84 ▴ 1.35</v>
       </c>
-      <c r="L35" s="11" t="str">
-        <f>TEXT(I7,"0.00") &amp; " ▴ " &amp; TEXT(J7,"0.00")</f>
+      <c r="L35" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>1.19 ▴ 1.78</v>
       </c>
-      <c r="M35" s="12" t="str">
-        <f>TEXT(I17,"0.00") &amp; " ▴ " &amp; TEXT(J17,"0.00")</f>
+      <c r="M35" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>1.18 ▴ 1.65</v>
       </c>
-      <c r="N35" s="11" t="str">
-        <f>TEXT(N7,"0.00") &amp; " ▴ " &amp; TEXT(O7,"0.00")</f>
+      <c r="N35" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>1.99 ▴ 2.57</v>
       </c>
-      <c r="O35" s="12" t="str">
-        <f>TEXT(N17,"0.00") &amp; " ▴ " &amp; TEXT(O17,"0.00")</f>
+      <c r="O35" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>1.80 ▴ 2.39</v>
       </c>
     </row>
@@ -5064,54 +4313,54 @@
         <v>4</v>
       </c>
       <c r="B36" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>5.4496091502550996</v>
       </c>
       <c r="C36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>4.2136905068906296</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>18.501208104486899</v>
       </c>
       <c r="E36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>19.2320751477234</v>
       </c>
       <c r="F36" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>15.838516178412601</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>16.4508394030658</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J36" s="11" t="str">
-        <f>TEXT(D8,"0.00") &amp; " ▴ " &amp; TEXT(E8,"0.00")</f>
+      <c r="J36" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>5.45 ▴ 8.59</v>
       </c>
-      <c r="K36" s="12" t="str">
-        <f>TEXT(D18,"0.00") &amp; " ▴ " &amp; TEXT(E18,"0.00")</f>
+      <c r="K36" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>4.21 ▴ 7.47</v>
       </c>
-      <c r="L36" s="11" t="str">
-        <f>TEXT(I8,"0.00") &amp; " ▴ " &amp; TEXT(J8,"0.00")</f>
+      <c r="L36" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>18.50 ▴ 24.52</v>
       </c>
-      <c r="M36" s="12" t="str">
-        <f>TEXT(I18,"0.00") &amp; " ▴ " &amp; TEXT(J18,"0.00")</f>
+      <c r="M36" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>19.23 ▴ 27.57</v>
       </c>
-      <c r="N36" s="11" t="str">
-        <f>TEXT(N8,"0.00") &amp; " ▴ " &amp; TEXT(O8,"0.00")</f>
+      <c r="N36" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>15.84 ▴ 22.33</v>
       </c>
-      <c r="O36" s="12" t="str">
-        <f>TEXT(N18,"0.00") &amp; " ▴ " &amp; TEXT(O18,"0.00")</f>
+      <c r="O36" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>16.45 ▴ 21.66</v>
       </c>
     </row>
@@ -5120,54 +4369,54 @@
         <v>5</v>
       </c>
       <c r="B37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>0.26300445032012498</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>0.34960681552240802</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>2.6760234679403698</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>2.64492250424887</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>3.2232238735838701</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>3.1473137309992398</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J37" s="11" t="str">
-        <f>TEXT(D9,"0.00") &amp; " ▴ " &amp; TEXT(E9,"0.00")</f>
+      <c r="J37" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>0.26 ▴ 0.96</v>
       </c>
-      <c r="K37" s="12" t="str">
-        <f>TEXT(D19,"0.00") &amp; " ▴ " &amp; TEXT(E19,"0.00")</f>
+      <c r="K37" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>0.35 ▴ 1.24</v>
       </c>
-      <c r="L37" s="11" t="str">
-        <f>TEXT(I9,"0.00") &amp; " ▴ " &amp; TEXT(J9,"0.00")</f>
+      <c r="L37" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>2.68 ▴ 4.34</v>
       </c>
-      <c r="M37" s="12" t="str">
-        <f>TEXT(I19,"0.00") &amp; " ▴ " &amp; TEXT(J19,"0.00")</f>
+      <c r="M37" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>2.64 ▴ 5.21</v>
       </c>
-      <c r="N37" s="11" t="str">
-        <f>TEXT(N9,"0.00") &amp; " ▴ " &amp; TEXT(O9,"0.00")</f>
+      <c r="N37" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>3.22 ▴ 4.31</v>
       </c>
-      <c r="O37" s="12" t="str">
-        <f>TEXT(N19,"0.00") &amp; " ▴ " &amp; TEXT(O19,"0.00")</f>
+      <c r="O37" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>3.15 ▴ 5.29</v>
       </c>
     </row>
@@ -5193,50 +4442,50 @@
     <mergeCell ref="N30:O30"/>
   </mergeCells>
   <conditionalFormatting sqref="J23:K28">
-    <cfRule type="expression" dxfId="78" priority="12">
+    <cfRule type="expression" dxfId="30" priority="12">
       <formula>($B23-$C23)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="13">
+    <cfRule type="expression" dxfId="29" priority="13">
       <formula>($B23-$C23)&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J32:K37">
+    <cfRule type="expression" dxfId="28" priority="5">
+      <formula>$B32-$C32&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="6">
+      <formula>$B32-$C32&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L23:M28">
-    <cfRule type="expression" dxfId="76" priority="10">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>$D23-$E23&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>$D23-$E23&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L32:M37">
+    <cfRule type="expression" dxfId="24" priority="3">
+      <formula>$D32-$E32&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="4">
+      <formula>$D32-$E32&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N23:O28">
-    <cfRule type="expression" dxfId="74" priority="7">
+    <cfRule type="expression" dxfId="22" priority="7">
       <formula>$F23-$G23&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="9">
+    <cfRule type="expression" dxfId="21" priority="9">
       <formula>$F23-$G23&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J32:K37">
-    <cfRule type="expression" dxfId="72" priority="5">
-      <formula>$B32-$C32&lt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="6">
-      <formula>$B32-$C32&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L32:M37">
-    <cfRule type="expression" dxfId="70" priority="3">
-      <formula>$D32-$E32&lt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="4">
-      <formula>$D32-$E32&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N32:O37">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>$F32-$G32&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>$F32-$G32&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5256,29 +4505,32 @@
       <c r="A1" t="s">
         <v>18</v>
       </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -5633,27 +4885,27 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -6040,18 +5292,18 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="17"/>
+      <c r="D22" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4" t="s">
+      <c r="E22" s="17"/>
+      <c r="F22" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="4"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -6095,22 +5347,22 @@
       <c r="A24" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="15">
         <v>1</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="16">
         <v>1.85997601300463E-38</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="15">
         <v>0</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="16">
         <v>0.54126184660139898</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="15">
         <v>1</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="16">
         <v>1.5053577318397299E-4</v>
       </c>
       <c r="H24" s="1"/>
@@ -6127,22 +5379,22 @@
       <c r="A25" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="15">
         <v>1</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="16">
         <v>1.5226779233754799E-11</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="15">
         <v>1</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="16">
         <v>9.8063131443357507E-15</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="15">
         <v>1</v>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="16">
         <v>3.0737935571875899E-28</v>
       </c>
       <c r="H25" s="1"/>
@@ -6159,22 +5411,22 @@
       <c r="A26" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="15">
         <v>1</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="16">
         <v>1.7359359790871899E-98</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="15">
         <v>1</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="16">
         <v>3.1211137802301198E-8</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="15">
         <v>1</v>
       </c>
-      <c r="G26" s="26">
+      <c r="G26" s="16">
         <v>6.1390299614830001E-74</v>
       </c>
       <c r="H26" s="1"/>
@@ -6191,22 +5443,22 @@
       <c r="A27" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="15">
         <v>1</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="16">
         <v>7.8450103677538799E-173</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="16">
         <v>7.7283916576270501E-7</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="16">
         <v>2.06114322140907E-34</v>
       </c>
       <c r="H27" s="1"/>
@@ -6223,22 +5475,22 @@
       <c r="A28" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="15">
         <v>1</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="16">
         <v>2.5240536099542802E-19</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="16">
         <v>1.3668713459711801E-2</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="15">
         <v>0</v>
       </c>
-      <c r="G28" s="26">
+      <c r="G28" s="16">
         <v>6.3146459475499003E-2</v>
       </c>
       <c r="H28" s="1"/>
@@ -6255,22 +5507,22 @@
       <c r="A29" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="15">
         <v>0</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="16">
         <v>8.4226018213132997E-2</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="15">
         <v>0</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="16">
         <v>0.17229992837017299</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="16">
         <v>5.4597335387266003E-3</v>
       </c>
       <c r="H29" s="1"/>
@@ -6284,12 +5536,12 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="26"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -6304,12 +5556,12 @@
       <c r="A31" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="26"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -6321,18 +5573,18 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="17"/>
+      <c r="F32" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="4"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -6376,22 +5628,22 @@
       <c r="A34" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="15">
         <v>1</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="16">
         <v>6.6804778712564598E-37</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="15">
         <v>0</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="16">
         <v>7.5810641888541294E-2</v>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="15">
         <v>1</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="16">
         <v>2.8673399772425798E-7</v>
       </c>
       <c r="H34" s="1"/>
@@ -6408,22 +5660,22 @@
       <c r="A35" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="15">
         <v>1</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="16">
         <v>1.2863176246777599E-4</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="15">
         <v>1</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="16">
         <v>2.43041337151972E-4</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="15">
         <v>1</v>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="16">
         <v>1.63216049154259E-24</v>
       </c>
       <c r="H35" s="1"/>
@@ -6440,22 +5692,22 @@
       <c r="A36" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="15">
         <v>1</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="16">
         <v>4.6674719784866803E-21</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="15">
         <v>1</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="16">
         <v>2.5724528187947599E-5</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="15">
         <v>1</v>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="16">
         <v>8.6565767890289508E-56</v>
       </c>
       <c r="H36" s="1"/>
@@ -6472,22 +5724,22 @@
       <c r="A37" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="15">
         <v>1</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="16">
         <v>1.5600389430414901E-126</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="15">
         <v>1</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="16">
         <v>1.4922728716519501E-4</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="15">
         <v>1</v>
       </c>
-      <c r="G37" s="26">
+      <c r="G37" s="16">
         <v>4.3440302970379702E-36</v>
       </c>
       <c r="H37" s="1"/>
@@ -6504,22 +5756,22 @@
       <c r="A38" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="15">
         <v>1</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="16">
         <v>7.7442346905808305E-24</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="15">
         <v>0</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="16">
         <v>0.114293128743026</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="15">
         <v>0</v>
       </c>
-      <c r="G38" s="26">
+      <c r="G38" s="16">
         <v>8.0610927049986E-2</v>
       </c>
       <c r="H38" s="1"/>
@@ -6536,22 +5788,22 @@
       <c r="A39" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="15">
         <v>1</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="16">
         <v>1.66985561900377E-4</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="15">
         <v>0</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="16">
         <v>0.97473314680503398</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="15">
         <v>0</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="16">
         <v>0.35317840771888598</v>
       </c>
       <c r="H39" s="1"/>
@@ -6565,33 +5817,35 @@
       <c r="P39" s="1"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="17"/>
+      <c r="D41" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4" t="s">
+      <c r="E41" s="17"/>
+      <c r="F41" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="9" t="s">
+      <c r="G41" s="17"/>
+      <c r="I41" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="J41" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="9" t="s">
+      <c r="K41" s="46"/>
+      <c r="L41" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="9" t="s">
+      <c r="M41" s="46"/>
+      <c r="N41" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="O41" s="10"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O41" s="46"/>
+    </row>
+    <row r="42" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>20</v>
       </c>
@@ -6610,23 +5864,23 @@
       <c r="G42" t="s">
         <v>21</v>
       </c>
-      <c r="I42" s="15"/>
-      <c r="J42" s="11" t="s">
+      <c r="I42" s="43"/>
+      <c r="J42" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="12" t="s">
+      <c r="K42" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="M42" s="12" t="s">
+      <c r="M42" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="N42" s="11" t="s">
+      <c r="N42" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O42" s="12" t="s">
+      <c r="O42" s="41" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6658,31 +5912,31 @@
         <f>L14</f>
         <v>6.0778871222411297</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="J43" s="11" t="str">
-        <f>TEXT(B4,"0.00") &amp; " ± " &amp; TEXT(C4,"0.00")</f>
+      <c r="J43" s="44" t="str">
+        <f t="shared" ref="J43:J48" si="0">TEXT(B4,"0.00") &amp; " ± " &amp; TEXT(C4,"0.00")</f>
         <v>3.21 ± 0.91</v>
       </c>
-      <c r="K43" s="12" t="str">
-        <f>TEXT(B14,"0.00") &amp; " ± " &amp; TEXT(C14,"0.00")</f>
+      <c r="K43" s="38" t="str">
+        <f t="shared" ref="K43:K48" si="1">TEXT(B14,"0.00") &amp; " ± " &amp; TEXT(C14,"0.00")</f>
         <v>4.09 ± 1.13</v>
       </c>
-      <c r="L43" s="11" t="str">
-        <f>TEXT(G4,"0.00") &amp; " ± " &amp; TEXT(H4,"0.00")</f>
+      <c r="L43" s="44" t="str">
+        <f t="shared" ref="L43:L48" si="2">TEXT(G4,"0.00") &amp; " ± " &amp; TEXT(H4,"0.00")</f>
         <v>6.65 ± 5.24</v>
       </c>
-      <c r="M43" s="12" t="str">
-        <f>TEXT(G14,"0.00") &amp; " ± " &amp; TEXT(H14,"0.00")</f>
+      <c r="M43" s="38" t="str">
+        <f t="shared" ref="M43:M48" si="3">TEXT(G14,"0.00") &amp; " ± " &amp; TEXT(H14,"0.00")</f>
         <v>6.07 ± 4.61</v>
       </c>
-      <c r="N43" s="11" t="str">
-        <f>TEXT(L4,"0.00") &amp; " ± " &amp; TEXT(M4,"0.00")</f>
+      <c r="N43" s="44" t="str">
+        <f t="shared" ref="N43:N48" si="4">TEXT(L4,"0.00") &amp; " ± " &amp; TEXT(M4,"0.00")</f>
         <v>5.29 ± 3.85</v>
       </c>
-      <c r="O43" s="12" t="str">
-        <f>TEXT(L14,"0.00") &amp; " ± " &amp; TEXT(M14,"0.00")</f>
+      <c r="O43" s="38" t="str">
+        <f t="shared" ref="O43:O48" si="5">TEXT(L14,"0.00") &amp; " ± " &amp; TEXT(M14,"0.00")</f>
         <v>6.08 ± 4.22</v>
       </c>
     </row>
@@ -6691,54 +5945,54 @@
         <v>1</v>
       </c>
       <c r="B44" s="1">
-        <f t="shared" ref="B44:B48" si="0">B5</f>
+        <f t="shared" ref="B44:B48" si="6">B5</f>
         <v>1.8272305635616399</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" ref="C44:C48" si="1">B15</f>
+        <f t="shared" ref="C44:C48" si="7">B15</f>
         <v>2.26330540363143</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" ref="D44:D48" si="2">G5</f>
+        <f t="shared" ref="D44:D48" si="8">G5</f>
         <v>7.0639384798379998</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" ref="E44:E48" si="3">G15</f>
+        <f t="shared" ref="E44:E48" si="9">G15</f>
         <v>6.5630790613226404</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" ref="F44:F48" si="4">L5</f>
+        <f t="shared" ref="F44:F48" si="10">L5</f>
         <v>6.1217279888108704</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" ref="G44:G48" si="5">L15</f>
+        <f t="shared" ref="G44:G48" si="11">L15</f>
         <v>7.0066382566082597</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J44" s="11" t="str">
-        <f>TEXT(B5,"0.00") &amp; " ± " &amp; TEXT(C5,"0.00")</f>
+      <c r="J44" s="6" t="str">
+        <f t="shared" si="0"/>
         <v>1.83 ± 1.26</v>
       </c>
-      <c r="K44" s="12" t="str">
-        <f>TEXT(B15,"0.00") &amp; " ± " &amp; TEXT(C15,"0.00")</f>
+      <c r="K44" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>2.26 ± 1.30</v>
       </c>
-      <c r="L44" s="11" t="str">
-        <f>TEXT(G5,"0.00") &amp; " ± " &amp; TEXT(H5,"0.00")</f>
+      <c r="L44" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>7.06 ± 1.36</v>
       </c>
-      <c r="M44" s="12" t="str">
-        <f>TEXT(G15,"0.00") &amp; " ± " &amp; TEXT(H15,"0.00")</f>
+      <c r="M44" s="7" t="str">
+        <f t="shared" si="3"/>
         <v>6.56 ± 1.55</v>
       </c>
-      <c r="N44" s="11" t="str">
-        <f>TEXT(L5,"0.00") &amp; " ± " &amp; TEXT(M5,"0.00")</f>
+      <c r="N44" s="6" t="str">
+        <f t="shared" si="4"/>
         <v>6.12 ± 1.70</v>
       </c>
-      <c r="O44" s="12" t="str">
-        <f>TEXT(L15,"0.00") &amp; " ± " &amp; TEXT(M15,"0.00")</f>
+      <c r="O44" s="7" t="str">
+        <f t="shared" si="5"/>
         <v>7.01 ± 1.69</v>
       </c>
     </row>
@@ -6747,54 +6001,54 @@
         <v>2</v>
       </c>
       <c r="B45" s="1">
+        <f t="shared" si="6"/>
+        <v>1.2815784691674601</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="7"/>
+        <v>0.76123516349491305</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="8"/>
+        <v>2.44907060232415</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" si="9"/>
+        <v>2.2515928648182499</v>
+      </c>
+      <c r="F45" s="1">
+        <f t="shared" si="10"/>
+        <v>3.85652302359202</v>
+      </c>
+      <c r="G45" s="1">
+        <f t="shared" si="11"/>
+        <v>2.7142584235473102</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>1.2815784691674601</v>
-      </c>
-      <c r="C45" s="1">
+        <v>1.28 ± 0.88</v>
+      </c>
+      <c r="K45" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0.76123516349491305</v>
-      </c>
-      <c r="D45" s="1">
+        <v>0.76 ± 0.74</v>
+      </c>
+      <c r="L45" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>2.44907060232415</v>
-      </c>
-      <c r="E45" s="1">
+        <v>2.45 ± 1.11</v>
+      </c>
+      <c r="M45" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>2.2515928648182499</v>
-      </c>
-      <c r="F45" s="1">
+        <v>2.25 ± 1.27</v>
+      </c>
+      <c r="N45" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3.85652302359202</v>
-      </c>
-      <c r="G45" s="1">
+        <v>3.86 ± 1.36</v>
+      </c>
+      <c r="O45" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>2.7142584235473102</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="J45" s="11" t="str">
-        <f>TEXT(B6,"0.00") &amp; " ± " &amp; TEXT(C6,"0.00")</f>
-        <v>1.28 ± 0.88</v>
-      </c>
-      <c r="K45" s="12" t="str">
-        <f>TEXT(B16,"0.00") &amp; " ± " &amp; TEXT(C16,"0.00")</f>
-        <v>0.76 ± 0.74</v>
-      </c>
-      <c r="L45" s="11" t="str">
-        <f>TEXT(G6,"0.00") &amp; " ± " &amp; TEXT(H6,"0.00")</f>
-        <v>2.45 ± 1.11</v>
-      </c>
-      <c r="M45" s="12" t="str">
-        <f>TEXT(G16,"0.00") &amp; " ± " &amp; TEXT(H16,"0.00")</f>
-        <v>2.25 ± 1.27</v>
-      </c>
-      <c r="N45" s="11" t="str">
-        <f>TEXT(L6,"0.00") &amp; " ± " &amp; TEXT(M6,"0.00")</f>
-        <v>3.86 ± 1.36</v>
-      </c>
-      <c r="O45" s="12" t="str">
-        <f>TEXT(L16,"0.00") &amp; " ± " &amp; TEXT(M16,"0.00")</f>
         <v>2.71 ± 1.24</v>
       </c>
     </row>
@@ -6803,54 +6057,54 @@
         <v>3</v>
       </c>
       <c r="B46" s="1">
+        <f t="shared" si="6"/>
+        <v>0.41377717832845101</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="7"/>
+        <v>0.85379028385400701</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="8"/>
+        <v>1.2215939217885099</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" si="9"/>
+        <v>1.16157293661143</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="10"/>
+        <v>1.9989106633526399</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" si="11"/>
+        <v>1.8021812002780599</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.41377717832845101</v>
-      </c>
-      <c r="C46" s="1">
+        <v>0.41 ± 0.27</v>
+      </c>
+      <c r="K46" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0.85379028385400701</v>
-      </c>
-      <c r="D46" s="1">
+        <v>0.85 ± 0.23</v>
+      </c>
+      <c r="L46" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>1.2215939217885099</v>
-      </c>
-      <c r="E46" s="1">
+        <v>1.22 ± 0.28</v>
+      </c>
+      <c r="M46" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.16157293661143</v>
-      </c>
-      <c r="F46" s="1">
+        <v>1.16 ± 0.31</v>
+      </c>
+      <c r="N46" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>1.9989106633526399</v>
-      </c>
-      <c r="G46" s="1">
+        <v>2.00 ± 0.33</v>
+      </c>
+      <c r="O46" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>1.8021812002780599</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="11" t="str">
-        <f>TEXT(B7,"0.00") &amp; " ± " &amp; TEXT(C7,"0.00")</f>
-        <v>0.41 ± 0.27</v>
-      </c>
-      <c r="K46" s="12" t="str">
-        <f>TEXT(B17,"0.00") &amp; " ± " &amp; TEXT(C17,"0.00")</f>
-        <v>0.85 ± 0.23</v>
-      </c>
-      <c r="L46" s="11" t="str">
-        <f>TEXT(G7,"0.00") &amp; " ± " &amp; TEXT(H7,"0.00")</f>
-        <v>1.22 ± 0.28</v>
-      </c>
-      <c r="M46" s="12" t="str">
-        <f>TEXT(G17,"0.00") &amp; " ± " &amp; TEXT(H17,"0.00")</f>
-        <v>1.16 ± 0.31</v>
-      </c>
-      <c r="N46" s="11" t="str">
-        <f>TEXT(L7,"0.00") &amp; " ± " &amp; TEXT(M7,"0.00")</f>
-        <v>2.00 ± 0.33</v>
-      </c>
-      <c r="O46" s="12" t="str">
-        <f>TEXT(L17,"0.00") &amp; " ± " &amp; TEXT(M17,"0.00")</f>
         <v>1.80 ± 0.33</v>
       </c>
     </row>
@@ -6859,54 +6113,54 @@
         <v>4</v>
       </c>
       <c r="B47" s="1">
+        <f t="shared" si="6"/>
+        <v>5.4646244811304303</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="7"/>
+        <v>4.2955416675485303</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="8"/>
+        <v>17.547896274193899</v>
+      </c>
+      <c r="E47" s="1">
+        <f t="shared" si="9"/>
+        <v>18.099372618286001</v>
+      </c>
+      <c r="F47" s="1">
+        <f t="shared" si="10"/>
+        <v>15.8315786186881</v>
+      </c>
+      <c r="G47" s="1">
+        <f t="shared" si="11"/>
+        <v>15.737257194167499</v>
+      </c>
+      <c r="I47" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>5.4646244811304303</v>
-      </c>
-      <c r="C47" s="1">
+        <v>5.46 ± 2.30</v>
+      </c>
+      <c r="K47" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>4.2955416675485303</v>
-      </c>
-      <c r="D47" s="1">
+        <v>4.30 ± 2.13</v>
+      </c>
+      <c r="L47" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>17.547896274193899</v>
-      </c>
-      <c r="E47" s="1">
+        <v>17.55 ± 7.86</v>
+      </c>
+      <c r="M47" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>18.099372618286001</v>
-      </c>
-      <c r="F47" s="1">
+        <v>18.10 ± 7.25</v>
+      </c>
+      <c r="N47" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>15.8315786186881</v>
-      </c>
-      <c r="G47" s="1">
+        <v>15.83 ± 4.42</v>
+      </c>
+      <c r="O47" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>15.737257194167499</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="11" t="str">
-        <f>TEXT(B8,"0.00") &amp; " ± " &amp; TEXT(C8,"0.00")</f>
-        <v>5.46 ± 2.30</v>
-      </c>
-      <c r="K47" s="12" t="str">
-        <f>TEXT(B18,"0.00") &amp; " ± " &amp; TEXT(C18,"0.00")</f>
-        <v>4.30 ± 2.13</v>
-      </c>
-      <c r="L47" s="11" t="str">
-        <f>TEXT(G8,"0.00") &amp; " ± " &amp; TEXT(H8,"0.00")</f>
-        <v>17.55 ± 7.86</v>
-      </c>
-      <c r="M47" s="12" t="str">
-        <f>TEXT(G18,"0.00") &amp; " ± " &amp; TEXT(H18,"0.00")</f>
-        <v>18.10 ± 7.25</v>
-      </c>
-      <c r="N47" s="11" t="str">
-        <f>TEXT(L8,"0.00") &amp; " ± " &amp; TEXT(M8,"0.00")</f>
-        <v>15.83 ± 4.42</v>
-      </c>
-      <c r="O47" s="12" t="str">
-        <f>TEXT(L18,"0.00") &amp; " ± " &amp; TEXT(M18,"0.00")</f>
         <v>15.74 ± 5.50</v>
       </c>
     </row>
@@ -6915,85 +6169,87 @@
         <v>5</v>
       </c>
       <c r="B48" s="1">
+        <f t="shared" si="6"/>
+        <v>0.45960260884256998</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="7"/>
+        <v>0.49745826098954499</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="8"/>
+        <v>2.6670859091564001</v>
+      </c>
+      <c r="E48" s="1">
+        <f t="shared" si="9"/>
+        <v>2.71459140188264</v>
+      </c>
+      <c r="F48" s="1">
+        <f t="shared" si="10"/>
+        <v>3.1487293164673198</v>
+      </c>
+      <c r="G48" s="1">
+        <f t="shared" si="11"/>
+        <v>3.13020600521227</v>
+      </c>
+      <c r="I48" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0.45960260884256998</v>
-      </c>
-      <c r="C48" s="1">
+        <v>0.46 ± 0.46</v>
+      </c>
+      <c r="K48" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>0.49745826098954499</v>
-      </c>
-      <c r="D48" s="1">
+        <v>0.50 ± 0.49</v>
+      </c>
+      <c r="L48" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>2.6670859091564001</v>
-      </c>
-      <c r="E48" s="1">
+        <v>2.67 ± 1.22</v>
+      </c>
+      <c r="M48" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>2.71459140188264</v>
-      </c>
-      <c r="F48" s="1">
+        <v>2.71 ± 1.17</v>
+      </c>
+      <c r="N48" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3.1487293164673198</v>
-      </c>
-      <c r="G48" s="1">
+        <v>3.15 ± 0.66</v>
+      </c>
+      <c r="O48" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>3.13020600521227</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="11" t="str">
-        <f>TEXT(B9,"0.00") &amp; " ± " &amp; TEXT(C9,"0.00")</f>
-        <v>0.46 ± 0.46</v>
-      </c>
-      <c r="K48" s="12" t="str">
-        <f>TEXT(B19,"0.00") &amp; " ± " &amp; TEXT(C19,"0.00")</f>
-        <v>0.50 ± 0.49</v>
-      </c>
-      <c r="L48" s="11" t="str">
-        <f>TEXT(G9,"0.00") &amp; " ± " &amp; TEXT(H9,"0.00")</f>
-        <v>2.67 ± 1.22</v>
-      </c>
-      <c r="M48" s="12" t="str">
-        <f>TEXT(G19,"0.00") &amp; " ± " &amp; TEXT(H19,"0.00")</f>
-        <v>2.71 ± 1.17</v>
-      </c>
-      <c r="N48" s="11" t="str">
-        <f>TEXT(L9,"0.00") &amp; " ± " &amp; TEXT(M9,"0.00")</f>
-        <v>3.15 ± 0.66</v>
-      </c>
-      <c r="O48" s="12" t="str">
-        <f>TEXT(L19,"0.00") &amp; " ± " &amp; TEXT(M19,"0.00")</f>
         <v>3.13 ± 1.01</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4" t="s">
+      <c r="C50" s="17"/>
+      <c r="D50" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
+      <c r="E50" s="17"/>
+      <c r="F50" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="4"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="9" t="s">
+      <c r="G50" s="17"/>
+      <c r="I50" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="9" t="s">
+      <c r="K50" s="46"/>
+      <c r="L50" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="9" t="s">
+      <c r="M50" s="46"/>
+      <c r="N50" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="O50" s="10"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="46"/>
+    </row>
+    <row r="51" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>20</v>
       </c>
@@ -7012,23 +6268,23 @@
       <c r="G51" t="s">
         <v>21</v>
       </c>
-      <c r="I51" s="15"/>
-      <c r="J51" s="11" t="s">
+      <c r="I51" s="43"/>
+      <c r="J51" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="M51" s="12" t="s">
+      <c r="M51" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="N51" s="11" t="s">
+      <c r="N51" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O51" s="12" t="s">
+      <c r="O51" s="41" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7060,31 +6316,31 @@
         <f>N14</f>
         <v>3.6630578537298102</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="I52" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="J52" s="11" t="str">
-        <f>TEXT(D4,"0.00") &amp; " ▴ " &amp; TEXT(E4,"0.00")</f>
+      <c r="J52" s="44" t="str">
+        <f t="shared" ref="J52:J57" si="12">TEXT(D4,"0.00") &amp; " ▴ " &amp; TEXT(E4,"0.00")</f>
         <v>2.87 ▴ 5.27</v>
       </c>
-      <c r="K52" s="12" t="str">
-        <f>TEXT(D14,"0.00") &amp; " ▴ " &amp; TEXT(E14,"0.00")</f>
+      <c r="K52" s="38" t="str">
+        <f t="shared" ref="K52:K57" si="13">TEXT(D14,"0.00") &amp; " ▴ " &amp; TEXT(E14,"0.00")</f>
         <v>3.87 ▴ 6.81</v>
       </c>
-      <c r="L52" s="11" t="str">
-        <f>TEXT(I4,"0.00") &amp; " ▴ " &amp; TEXT(J4,"0.00")</f>
+      <c r="L52" s="44" t="str">
+        <f t="shared" ref="L52:L57" si="14">TEXT(I4,"0.00") &amp; " ▴ " &amp; TEXT(J4,"0.00")</f>
         <v>1.67 ▴ 17.07</v>
       </c>
-      <c r="M52" s="12" t="str">
-        <f>TEXT(I14,"0.00") &amp; " ▴ " &amp; TEXT(J14,"0.00")</f>
+      <c r="M52" s="38" t="str">
+        <f t="shared" ref="M52:M57" si="15">TEXT(I14,"0.00") &amp; " ▴ " &amp; TEXT(J14,"0.00")</f>
         <v>2.86 ▴ 14.53</v>
       </c>
-      <c r="N52" s="11" t="str">
-        <f>TEXT(N4,"0.00") &amp; " ▴ " &amp; TEXT(O4,"0.00")</f>
+      <c r="N52" s="44" t="str">
+        <f t="shared" ref="N52:N57" si="16">TEXT(N4,"0.00") &amp; " ▴ " &amp; TEXT(O4,"0.00")</f>
         <v>2.39 ▴ 13.05</v>
       </c>
-      <c r="O52" s="12" t="str">
-        <f>TEXT(N14,"0.00") &amp; " ▴ " &amp; TEXT(O14,"0.00")</f>
+      <c r="O52" s="38" t="str">
+        <f t="shared" ref="O52:O57" si="17">TEXT(N14,"0.00") &amp; " ▴ " &amp; TEXT(O14,"0.00")</f>
         <v>3.66 ▴ 11.92</v>
       </c>
     </row>
@@ -7093,54 +6349,54 @@
         <v>1</v>
       </c>
       <c r="B53" s="1">
-        <f t="shared" ref="B53:B57" si="6">D5</f>
+        <f t="shared" ref="B53:B57" si="18">D5</f>
         <v>1.3433967767398101</v>
       </c>
       <c r="C53" s="1">
-        <f t="shared" ref="C53:C57" si="7">D15</f>
+        <f t="shared" ref="C53:C57" si="19">D15</f>
         <v>1.7267247613207899</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" ref="D53:D57" si="8">I5</f>
+        <f t="shared" ref="D53:D57" si="20">I5</f>
         <v>6.7091501687396597</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" ref="E53:E57" si="9">I15</f>
+        <f t="shared" ref="E53:E57" si="21">I15</f>
         <v>6.5875819010309602</v>
       </c>
       <c r="F53" s="1">
-        <f t="shared" ref="F53:F57" si="10">N5</f>
+        <f t="shared" ref="F53:F57" si="22">N5</f>
         <v>6.0693888007527299</v>
       </c>
       <c r="G53" s="1">
-        <f t="shared" ref="G53:G57" si="11">N15</f>
+        <f t="shared" ref="G53:G57" si="23">N15</f>
         <v>6.6377020590646802</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="I53" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J53" s="11" t="str">
-        <f>TEXT(D5,"0.00") &amp; " ▴ " &amp; TEXT(E5,"0.00")</f>
+      <c r="J53" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>1.34 ▴ 4.06</v>
       </c>
-      <c r="K53" s="12" t="str">
-        <f>TEXT(D15,"0.00") &amp; " ▴ " &amp; TEXT(E15,"0.00")</f>
+      <c r="K53" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>1.73 ▴ 4.37</v>
       </c>
-      <c r="L53" s="11" t="str">
-        <f>TEXT(I5,"0.00") &amp; " ▴ " &amp; TEXT(J5,"0.00")</f>
+      <c r="L53" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>6.71 ▴ 10.04</v>
       </c>
-      <c r="M53" s="12" t="str">
-        <f>TEXT(I15,"0.00") &amp; " ▴ " &amp; TEXT(J15,"0.00")</f>
+      <c r="M53" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>6.59 ▴ 9.02</v>
       </c>
-      <c r="N53" s="11" t="str">
-        <f>TEXT(N5,"0.00") &amp; " ▴ " &amp; TEXT(O5,"0.00")</f>
+      <c r="N53" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>6.07 ▴ 10.15</v>
       </c>
-      <c r="O53" s="12" t="str">
-        <f>TEXT(N15,"0.00") &amp; " ▴ " &amp; TEXT(O15,"0.00")</f>
+      <c r="O53" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>6.64 ▴ 11.06</v>
       </c>
     </row>
@@ -7149,54 +6405,54 @@
         <v>2</v>
       </c>
       <c r="B54" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>1.00507089517066</v>
       </c>
       <c r="C54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>0.53522748019432598</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>2.2640863509146101</v>
       </c>
       <c r="E54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>2.1095362189402298</v>
       </c>
       <c r="F54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>3.4661718529955499</v>
       </c>
       <c r="G54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>2.6486084869154398</v>
       </c>
-      <c r="I54" s="15" t="s">
+      <c r="I54" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="J54" s="11" t="str">
-        <f>TEXT(D6,"0.00") &amp; " ▴ " &amp; TEXT(E6,"0.00")</f>
+      <c r="J54" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>1.01 ▴ 3.11</v>
       </c>
-      <c r="K54" s="12" t="str">
-        <f>TEXT(D16,"0.00") &amp; " ▴ " &amp; TEXT(E16,"0.00")</f>
+      <c r="K54" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>0.54 ▴ 1.61</v>
       </c>
-      <c r="L54" s="11" t="str">
-        <f>TEXT(I6,"0.00") &amp; " ▴ " &amp; TEXT(J6,"0.00")</f>
+      <c r="L54" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>2.26 ▴ 4.43</v>
       </c>
-      <c r="M54" s="12" t="str">
-        <f>TEXT(I16,"0.00") &amp; " ▴ " &amp; TEXT(J16,"0.00")</f>
+      <c r="M54" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>2.11 ▴ 4.01</v>
       </c>
-      <c r="N54" s="11" t="str">
-        <f>TEXT(N6,"0.00") &amp; " ▴ " &amp; TEXT(O6,"0.00")</f>
+      <c r="N54" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>3.47 ▴ 6.04</v>
       </c>
-      <c r="O54" s="12" t="str">
-        <f>TEXT(N16,"0.00") &amp; " ▴ " &amp; TEXT(O16,"0.00")</f>
+      <c r="O54" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>2.65 ▴ 4.65</v>
       </c>
     </row>
@@ -7205,54 +6461,54 @@
         <v>3</v>
       </c>
       <c r="B55" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>0.27054172691310202</v>
       </c>
       <c r="C55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>0.84387955346518195</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>1.19193064784142</v>
       </c>
       <c r="E55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>1.1827980487996701</v>
       </c>
       <c r="F55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>1.9932274136964001</v>
       </c>
       <c r="G55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>1.8032077594970399</v>
       </c>
-      <c r="I55" s="15" t="s">
+      <c r="I55" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="J55" s="11" t="str">
-        <f>TEXT(D7,"0.00") &amp; " ▴ " &amp; TEXT(E7,"0.00")</f>
+      <c r="J55" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>0.27 ▴ 0.93</v>
       </c>
-      <c r="K55" s="12" t="str">
-        <f>TEXT(D17,"0.00") &amp; " ▴ " &amp; TEXT(E17,"0.00")</f>
+      <c r="K55" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>0.84 ▴ 1.35</v>
       </c>
-      <c r="L55" s="11" t="str">
-        <f>TEXT(I7,"0.00") &amp; " ▴ " &amp; TEXT(J7,"0.00")</f>
+      <c r="L55" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>1.19 ▴ 1.78</v>
       </c>
-      <c r="M55" s="12" t="str">
-        <f>TEXT(I17,"0.00") &amp; " ▴ " &amp; TEXT(J17,"0.00")</f>
+      <c r="M55" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>1.18 ▴ 1.65</v>
       </c>
-      <c r="N55" s="11" t="str">
-        <f>TEXT(N7,"0.00") &amp; " ▴ " &amp; TEXT(O7,"0.00")</f>
+      <c r="N55" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>1.99 ▴ 2.57</v>
       </c>
-      <c r="O55" s="12" t="str">
-        <f>TEXT(N17,"0.00") &amp; " ▴ " &amp; TEXT(O17,"0.00")</f>
+      <c r="O55" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>1.80 ▴ 2.39</v>
       </c>
     </row>
@@ -7261,54 +6517,54 @@
         <v>4</v>
       </c>
       <c r="B56" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>5.4496091502550996</v>
       </c>
       <c r="C56" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>4.2136905068906296</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>18.501208104486899</v>
       </c>
       <c r="E56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>19.2320751477234</v>
       </c>
       <c r="F56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>15.838516178412601</v>
       </c>
       <c r="G56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>16.4508394030658</v>
       </c>
-      <c r="I56" s="15" t="s">
+      <c r="I56" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J56" s="11" t="str">
-        <f>TEXT(D8,"0.00") &amp; " ▴ " &amp; TEXT(E8,"0.00")</f>
+      <c r="J56" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>5.45 ▴ 8.59</v>
       </c>
-      <c r="K56" s="12" t="str">
-        <f>TEXT(D18,"0.00") &amp; " ▴ " &amp; TEXT(E18,"0.00")</f>
+      <c r="K56" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>4.21 ▴ 7.47</v>
       </c>
-      <c r="L56" s="11" t="str">
-        <f>TEXT(I8,"0.00") &amp; " ▴ " &amp; TEXT(J8,"0.00")</f>
+      <c r="L56" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>18.50 ▴ 24.52</v>
       </c>
-      <c r="M56" s="12" t="str">
-        <f>TEXT(I18,"0.00") &amp; " ▴ " &amp; TEXT(J18,"0.00")</f>
+      <c r="M56" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>19.23 ▴ 27.57</v>
       </c>
-      <c r="N56" s="11" t="str">
-        <f>TEXT(N8,"0.00") &amp; " ▴ " &amp; TEXT(O8,"0.00")</f>
+      <c r="N56" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>15.84 ▴ 22.33</v>
       </c>
-      <c r="O56" s="12" t="str">
-        <f>TEXT(N18,"0.00") &amp; " ▴ " &amp; TEXT(O18,"0.00")</f>
+      <c r="O56" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>16.45 ▴ 21.66</v>
       </c>
     </row>
@@ -7317,70 +6573,65 @@
         <v>5</v>
       </c>
       <c r="B57" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>0.26300445032012498</v>
       </c>
       <c r="C57" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>0.34960681552240802</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>2.6760234679403698</v>
       </c>
       <c r="E57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>2.64492250424887</v>
       </c>
       <c r="F57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>3.2232238735838701</v>
       </c>
       <c r="G57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>3.1473137309992398</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="I57" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J57" s="11" t="str">
-        <f>TEXT(D9,"0.00") &amp; " ▴ " &amp; TEXT(E9,"0.00")</f>
+      <c r="J57" s="6" t="str">
+        <f t="shared" si="12"/>
         <v>0.26 ▴ 0.96</v>
       </c>
-      <c r="K57" s="12" t="str">
-        <f>TEXT(D19,"0.00") &amp; " ▴ " &amp; TEXT(E19,"0.00")</f>
+      <c r="K57" s="7" t="str">
+        <f t="shared" si="13"/>
         <v>0.35 ▴ 1.24</v>
       </c>
-      <c r="L57" s="11" t="str">
-        <f>TEXT(I9,"0.00") &amp; " ▴ " &amp; TEXT(J9,"0.00")</f>
+      <c r="L57" s="6" t="str">
+        <f t="shared" si="14"/>
         <v>2.68 ▴ 4.34</v>
       </c>
-      <c r="M57" s="12" t="str">
-        <f>TEXT(I19,"0.00") &amp; " ▴ " &amp; TEXT(J19,"0.00")</f>
+      <c r="M57" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>2.64 ▴ 5.21</v>
       </c>
-      <c r="N57" s="11" t="str">
-        <f>TEXT(N9,"0.00") &amp; " ▴ " &amp; TEXT(O9,"0.00")</f>
+      <c r="N57" s="6" t="str">
+        <f t="shared" si="16"/>
         <v>3.22 ▴ 4.31</v>
       </c>
-      <c r="O57" s="12" t="str">
-        <f>TEXT(N19,"0.00") &amp; " ▴ " &amp; TEXT(O19,"0.00")</f>
+      <c r="O57" s="7" t="str">
+        <f t="shared" si="17"/>
         <v>3.15 ▴ 5.29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="L50:M50"/>
     <mergeCell ref="N50:O50"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D41:E41"/>
@@ -7388,6 +6639,13 @@
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="N41:O41"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I50:I51"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="L2:P2"/>
@@ -7395,70 +6653,70 @@
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="L12:P12"/>
   </mergeCells>
+  <conditionalFormatting sqref="J43:K48">
+    <cfRule type="expression" dxfId="18" priority="100" stopIfTrue="1">
+      <formula>($B24=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="101">
+      <formula>($B43-$C43)&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="102">
+      <formula>($B43-$C43)&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J52:K57">
-    <cfRule type="expression" dxfId="34" priority="11">
+    <cfRule type="expression" dxfId="15" priority="3" stopIfTrue="1">
+      <formula>$B34=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>$B52-$C52&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="12">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>$B52-$C52&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="3" stopIfTrue="1">
-      <formula>$B34=0</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L43:M48">
+    <cfRule type="expression" dxfId="12" priority="103" stopIfTrue="1">
+      <formula>$D24=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="104">
+      <formula>$D43-$E43&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="105">
+      <formula>$D43-$E43&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:M57">
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="9" priority="2" stopIfTrue="1">
+      <formula>$D34=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$D52-$E52&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="10">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>$D52-$E52&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="2" stopIfTrue="1">
-      <formula>$D34=0</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N43:O48">
+    <cfRule type="expression" dxfId="6" priority="106" stopIfTrue="1">
+      <formula>$F24=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="107">
+      <formula>$F43-$G43&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="108">
+      <formula>$F43-$G43&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N52:O57">
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$F34=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>$F52-$G52&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>$F52-$G52&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="1" stopIfTrue="1">
-      <formula>$F34=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J43:K48">
-    <cfRule type="expression" dxfId="28" priority="100" stopIfTrue="1">
-      <formula>($B24=0)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="101">
-      <formula>($B43-$C43)&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="102">
-      <formula>($B43-$C43)&lt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L43:M48">
-    <cfRule type="expression" dxfId="25" priority="103" stopIfTrue="1">
-      <formula>$D24=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="104">
-      <formula>$D43-$E43&lt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="105">
-      <formula>$D43-$E43&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N43:O48">
-    <cfRule type="expression" dxfId="22" priority="106" stopIfTrue="1">
-      <formula>$F24=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="107">
-      <formula>$F43-$G43&lt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="108">
-      <formula>$F43-$G43&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7475,24 +6733,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="17"/>
+      <c r="F1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -7524,28 +6782,28 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1.5950326481907</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.191615948098493</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>1.49974894766178</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.16887778112778401</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>1.21188744894645</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>0.16491021443244899</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>0.93239369238328595</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.24046268546746499</v>
       </c>
     </row>
@@ -7553,122 +6811,120 @@
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>4.2612260838798903</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.25647923273703299</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>3.76412833012323</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.47329103879545997</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>3.6828805773637399</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>0.50470634581892904</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1.70779155788536</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>0.433397838553298</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="24" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f>B3</f>
         <v>1.5950326481907</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f>D3</f>
         <v>1.49974894766178</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f>F3</f>
         <v>1.21188744894645</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <f>H3</f>
         <v>0.93239369238328595</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>B4</f>
         <v>4.2612260838798903</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f>D4</f>
         <v>3.76412833012323</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>F4</f>
         <v>3.6828805773637399</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <f>H4</f>
         <v>1.70779155788536</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="24" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="6" t="str">
+      <c r="B11" s="4" t="str">
         <f>TEXT(B3,"0.00") &amp; " ± " &amp; TEXT(C3,"0.00")</f>
         <v>1.60 ± 0.19</v>
       </c>
-      <c r="C11" s="6" t="str">
+      <c r="C11" s="4" t="str">
         <f>TEXT(D3,"0.00") &amp; " ± " &amp; TEXT(E3,"0.00")</f>
         <v>1.50 ± 0.17</v>
       </c>
-      <c r="D11" s="6" t="str">
+      <c r="D11" s="4" t="str">
         <f>TEXT(F3,"0.00") &amp; " ± " &amp; TEXT(G3,"0.00")</f>
         <v>1.21 ± 0.16</v>
       </c>
-      <c r="E11" s="20" t="str">
+      <c r="E11" s="12" t="str">
         <f>TEXT(H3,"0.00") &amp; " ± " &amp; TEXT(I3,"0.00")</f>
         <v>0.93 ± 0.24</v>
       </c>
@@ -7677,22 +6933,22 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="6" t="str">
+      <c r="B12" s="4" t="str">
         <f>TEXT(B4,"0.00") &amp; " ± " &amp; TEXT(C4,"0.00")</f>
         <v>4.26 ± 0.26</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" s="4" t="str">
         <f>TEXT(D4,"0.00") &amp; " ± " &amp; TEXT(E4,"0.00")</f>
         <v>3.76 ± 0.47</v>
       </c>
-      <c r="D12" s="6" t="str">
+      <c r="D12" s="4" t="str">
         <f>TEXT(F4,"0.00") &amp; " ± " &amp; TEXT(G4,"0.00")</f>
         <v>3.68 ± 0.50</v>
       </c>
-      <c r="E12" s="20" t="str">
+      <c r="E12" s="12" t="str">
         <f>TEXT(H4,"0.00") &amp; " ± " &amp; TEXT(I4,"0.00")</f>
         <v>1.71 ± 0.43</v>
       </c>
@@ -7706,7 +6962,7 @@
     <mergeCell ref="J1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:E8">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>B7=MIN($B7:$E7)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/outputs/tablestat_template.xlsx
+++ b/outputs/tablestat_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\BELANDA\PhD Thesis\Code\MATLAB\amode_navigation_experiment\experiment_b\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373B26CE-338E-419B-AB41-19D3BBCC2BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CA7AE9-76F4-4722-9FA9-C97FFDA99F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B592097C-7DAF-4CBB-990E-BEE084540A4C}"/>
+    <workbookView xWindow="-23136" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="3" xr2:uid="{B592097C-7DAF-4CBB-990E-BEE084540A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="kinematicEval" sheetId="1" r:id="rId1"/>
@@ -442,18 +442,6 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -467,24 +455,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -503,21 +473,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1165,41 +1165,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17" t="s">
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="18" t="s">
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18" t="s">
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -1699,31 +1699,31 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="18" t="s">
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18" t="s">
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -2174,22 +2174,22 @@
       <c r="P18" s="2"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="26" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="26" t="s">
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="27"/>
-      <c r="J19" s="28"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="41"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
@@ -2198,32 +2198,32 @@
       <c r="P19" s="2"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="24" t="s">
+      <c r="I20" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="25" t="s">
+      <c r="J20" s="21" t="s">
         <v>13</v>
       </c>
       <c r="K20" s="2"/>
@@ -2516,95 +2516,95 @@
       <c r="P26" s="2"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="29" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="29" t="s">
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="30"/>
-      <c r="J28" s="31"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="38"/>
       <c r="L28" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="43"/>
-      <c r="B29" s="39" t="s">
+      <c r="A29" s="35"/>
+      <c r="B29" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="39" t="s">
+      <c r="E29" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="39" t="s">
+      <c r="H29" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="I29" s="40" t="s">
+      <c r="I29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J29" s="41" t="s">
+      <c r="J29" s="31" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="33" t="str">
+      <c r="B30" s="23" t="str">
         <f>B12</f>
         <v>3.70 ± 1.06</v>
       </c>
-      <c r="C30" s="34" t="str">
+      <c r="C30" s="24" t="str">
         <f>E12</f>
         <v>6.71 ± 5.13</v>
       </c>
-      <c r="D30" s="35" t="str">
+      <c r="D30" s="25" t="str">
         <f>H12</f>
         <v>5.53 ± 3.92</v>
       </c>
-      <c r="E30" s="36" t="str">
+      <c r="E30" s="26" t="str">
         <f>C12</f>
         <v>3.37 ▴ 6.79</v>
       </c>
-      <c r="F30" s="37" t="str">
+      <c r="F30" s="27" t="str">
         <f>F12</f>
         <v>2.66 ▴ 17.08</v>
       </c>
-      <c r="G30" s="38" t="str">
+      <c r="G30" s="28" t="str">
         <f>I12</f>
         <v>2.96 ▴ 13.05</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="23">
         <f>D12</f>
         <v>0.99600004112783203</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="24">
         <f>G12</f>
         <v>0.98133763413798303</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="25">
         <f>J12</f>
         <v>0.99055095826475403</v>
       </c>
@@ -2816,6 +2816,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:G28"/>
@@ -2823,16 +2833,6 @@
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="V1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="B21:D26">
     <cfRule type="expression" dxfId="34" priority="4">
@@ -2872,27 +2872,27 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17" t="s">
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -3247,27 +3247,27 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17" t="s">
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -3617,31 +3617,31 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17" t="s">
+      <c r="C21" s="42"/>
+      <c r="D21" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17" t="s">
+      <c r="E21" s="42"/>
+      <c r="F21" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="17"/>
+      <c r="G21" s="42"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="45"/>
+      <c r="L21" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="19" t="s">
+      <c r="M21" s="45"/>
+      <c r="N21" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="O21" s="20"/>
+      <c r="O21" s="45"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
@@ -4019,31 +4019,31 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17" t="s">
+      <c r="C30" s="42"/>
+      <c r="D30" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17" t="s">
+      <c r="E30" s="42"/>
+      <c r="F30" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="17"/>
+      <c r="G30" s="42"/>
       <c r="I30" s="10"/>
-      <c r="J30" s="19" t="s">
+      <c r="J30" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="K30" s="20"/>
-      <c r="L30" s="19" t="s">
+      <c r="K30" s="45"/>
+      <c r="L30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="M30" s="20"/>
-      <c r="N30" s="19" t="s">
+      <c r="M30" s="45"/>
+      <c r="N30" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="O30" s="20"/>
+      <c r="O30" s="45"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
@@ -4422,24 +4422,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="L12:P12"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="L12:P12"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="N30:O30"/>
   </mergeCells>
   <conditionalFormatting sqref="J23:K28">
     <cfRule type="expression" dxfId="30" priority="12">
@@ -4510,27 +4510,27 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17" t="s">
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -4885,27 +4885,27 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17" t="s">
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -5292,18 +5292,18 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17" t="s">
+      <c r="C22" s="42"/>
+      <c r="D22" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17" t="s">
+      <c r="E22" s="42"/>
+      <c r="F22" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -5573,18 +5573,18 @@
       <c r="P31" s="1"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17" t="s">
+      <c r="E32" s="42"/>
+      <c r="F32" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="17"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -5817,33 +5817,33 @@
       <c r="P39" s="1"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17" t="s">
+      <c r="C41" s="42"/>
+      <c r="D41" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17" t="s">
+      <c r="E41" s="42"/>
+      <c r="F41" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="17"/>
-      <c r="I41" s="42" t="s">
+      <c r="G41" s="42"/>
+      <c r="I41" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="45" t="s">
+      <c r="J41" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="K41" s="46"/>
-      <c r="L41" s="45" t="s">
+      <c r="K41" s="47"/>
+      <c r="L41" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M41" s="46"/>
-      <c r="N41" s="45" t="s">
+      <c r="M41" s="47"/>
+      <c r="N41" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="O41" s="46"/>
+      <c r="O41" s="47"/>
     </row>
     <row r="42" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
@@ -5864,23 +5864,23 @@
       <c r="G42" t="s">
         <v>21</v>
       </c>
-      <c r="I42" s="43"/>
-      <c r="J42" s="39" t="s">
+      <c r="I42" s="35"/>
+      <c r="J42" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="41" t="s">
+      <c r="K42" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="L42" s="39" t="s">
+      <c r="L42" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="M42" s="41" t="s">
+      <c r="M42" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="N42" s="39" t="s">
+      <c r="N42" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="O42" s="41" t="s">
+      <c r="O42" s="31" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5912,30 +5912,30 @@
         <f>L14</f>
         <v>6.0778871222411297</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="J43" s="44" t="str">
+      <c r="J43" s="32" t="str">
         <f t="shared" ref="J43:J48" si="0">TEXT(B4,"0.00") &amp; " ± " &amp; TEXT(C4,"0.00")</f>
         <v>3.21 ± 0.91</v>
       </c>
-      <c r="K43" s="38" t="str">
+      <c r="K43" s="28" t="str">
         <f t="shared" ref="K43:K48" si="1">TEXT(B14,"0.00") &amp; " ± " &amp; TEXT(C14,"0.00")</f>
         <v>4.09 ± 1.13</v>
       </c>
-      <c r="L43" s="44" t="str">
+      <c r="L43" s="32" t="str">
         <f t="shared" ref="L43:L48" si="2">TEXT(G4,"0.00") &amp; " ± " &amp; TEXT(H4,"0.00")</f>
         <v>6.65 ± 5.24</v>
       </c>
-      <c r="M43" s="38" t="str">
+      <c r="M43" s="28" t="str">
         <f t="shared" ref="M43:M48" si="3">TEXT(G14,"0.00") &amp; " ± " &amp; TEXT(H14,"0.00")</f>
         <v>6.07 ± 4.61</v>
       </c>
-      <c r="N43" s="44" t="str">
+      <c r="N43" s="32" t="str">
         <f t="shared" ref="N43:N48" si="4">TEXT(L4,"0.00") &amp; " ± " &amp; TEXT(M4,"0.00")</f>
         <v>5.29 ± 3.85</v>
       </c>
-      <c r="O43" s="38" t="str">
+      <c r="O43" s="28" t="str">
         <f t="shared" ref="O43:O48" si="5">TEXT(L14,"0.00") &amp; " ± " &amp; TEXT(M14,"0.00")</f>
         <v>6.08 ± 4.22</v>
       </c>
@@ -5968,7 +5968,7 @@
         <f t="shared" ref="G44:G48" si="11">L15</f>
         <v>7.0066382566082597</v>
       </c>
-      <c r="I44" s="21" t="s">
+      <c r="I44" s="17" t="s">
         <v>1</v>
       </c>
       <c r="J44" s="6" t="str">
@@ -6024,7 +6024,7 @@
         <f t="shared" si="11"/>
         <v>2.7142584235473102</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="I45" s="17" t="s">
         <v>2</v>
       </c>
       <c r="J45" s="6" t="str">
@@ -6080,7 +6080,7 @@
         <f t="shared" si="11"/>
         <v>1.8021812002780599</v>
       </c>
-      <c r="I46" s="21" t="s">
+      <c r="I46" s="17" t="s">
         <v>3</v>
       </c>
       <c r="J46" s="6" t="str">
@@ -6136,7 +6136,7 @@
         <f t="shared" si="11"/>
         <v>15.737257194167499</v>
       </c>
-      <c r="I47" s="21" t="s">
+      <c r="I47" s="17" t="s">
         <v>4</v>
       </c>
       <c r="J47" s="6" t="str">
@@ -6192,7 +6192,7 @@
         <f t="shared" si="11"/>
         <v>3.13020600521227</v>
       </c>
-      <c r="I48" s="21" t="s">
+      <c r="I48" s="17" t="s">
         <v>5</v>
       </c>
       <c r="J48" s="6" t="str">
@@ -6221,33 +6221,33 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17" t="s">
+      <c r="C50" s="42"/>
+      <c r="D50" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17" t="s">
+      <c r="E50" s="42"/>
+      <c r="F50" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="17"/>
-      <c r="I50" s="42" t="s">
+      <c r="G50" s="42"/>
+      <c r="I50" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="J50" s="45" t="s">
+      <c r="J50" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="K50" s="46"/>
-      <c r="L50" s="45" t="s">
+      <c r="K50" s="47"/>
+      <c r="L50" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M50" s="46"/>
-      <c r="N50" s="45" t="s">
+      <c r="M50" s="47"/>
+      <c r="N50" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="O50" s="46"/>
+      <c r="O50" s="47"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
@@ -6268,23 +6268,23 @@
       <c r="G51" t="s">
         <v>21</v>
       </c>
-      <c r="I51" s="43"/>
-      <c r="J51" s="39" t="s">
+      <c r="I51" s="35"/>
+      <c r="J51" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="K51" s="41" t="s">
+      <c r="K51" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="L51" s="39" t="s">
+      <c r="L51" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="M51" s="41" t="s">
+      <c r="M51" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="N51" s="39" t="s">
+      <c r="N51" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="O51" s="41" t="s">
+      <c r="O51" s="31" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6316,30 +6316,30 @@
         <f>N14</f>
         <v>3.6630578537298102</v>
       </c>
-      <c r="I52" s="47" t="s">
+      <c r="I52" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="J52" s="44" t="str">
+      <c r="J52" s="32" t="str">
         <f t="shared" ref="J52:J57" si="12">TEXT(D4,"0.00") &amp; " ▴ " &amp; TEXT(E4,"0.00")</f>
         <v>2.87 ▴ 5.27</v>
       </c>
-      <c r="K52" s="38" t="str">
+      <c r="K52" s="28" t="str">
         <f t="shared" ref="K52:K57" si="13">TEXT(D14,"0.00") &amp; " ▴ " &amp; TEXT(E14,"0.00")</f>
         <v>3.87 ▴ 6.81</v>
       </c>
-      <c r="L52" s="44" t="str">
+      <c r="L52" s="32" t="str">
         <f t="shared" ref="L52:L57" si="14">TEXT(I4,"0.00") &amp; " ▴ " &amp; TEXT(J4,"0.00")</f>
         <v>1.67 ▴ 17.07</v>
       </c>
-      <c r="M52" s="38" t="str">
+      <c r="M52" s="28" t="str">
         <f t="shared" ref="M52:M57" si="15">TEXT(I14,"0.00") &amp; " ▴ " &amp; TEXT(J14,"0.00")</f>
         <v>2.86 ▴ 14.53</v>
       </c>
-      <c r="N52" s="44" t="str">
+      <c r="N52" s="32" t="str">
         <f t="shared" ref="N52:N57" si="16">TEXT(N4,"0.00") &amp; " ▴ " &amp; TEXT(O4,"0.00")</f>
         <v>2.39 ▴ 13.05</v>
       </c>
-      <c r="O52" s="38" t="str">
+      <c r="O52" s="28" t="str">
         <f t="shared" ref="O52:O57" si="17">TEXT(N14,"0.00") &amp; " ▴ " &amp; TEXT(O14,"0.00")</f>
         <v>3.66 ▴ 11.92</v>
       </c>
@@ -6372,7 +6372,7 @@
         <f t="shared" ref="G53:G57" si="23">N15</f>
         <v>6.6377020590646802</v>
       </c>
-      <c r="I53" s="21" t="s">
+      <c r="I53" s="17" t="s">
         <v>1</v>
       </c>
       <c r="J53" s="6" t="str">
@@ -6428,7 +6428,7 @@
         <f t="shared" si="23"/>
         <v>2.6486084869154398</v>
       </c>
-      <c r="I54" s="21" t="s">
+      <c r="I54" s="17" t="s">
         <v>2</v>
       </c>
       <c r="J54" s="6" t="str">
@@ -6484,7 +6484,7 @@
         <f t="shared" si="23"/>
         <v>1.8032077594970399</v>
       </c>
-      <c r="I55" s="21" t="s">
+      <c r="I55" s="17" t="s">
         <v>3</v>
       </c>
       <c r="J55" s="6" t="str">
@@ -6540,7 +6540,7 @@
         <f t="shared" si="23"/>
         <v>16.4508394030658</v>
       </c>
-      <c r="I56" s="21" t="s">
+      <c r="I56" s="17" t="s">
         <v>4</v>
       </c>
       <c r="J56" s="6" t="str">
@@ -6596,7 +6596,7 @@
         <f t="shared" si="23"/>
         <v>3.1473137309992398</v>
       </c>
-      <c r="I57" s="21" t="s">
+      <c r="I57" s="17" t="s">
         <v>5</v>
       </c>
       <c r="J57" s="6" t="str">
@@ -6626,12 +6626,12 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="L12:P12"/>
     <mergeCell ref="N50:O50"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D41:E41"/>
@@ -6646,12 +6646,12 @@
     <mergeCell ref="L50:M50"/>
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="I50:I51"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
   </mergeCells>
   <conditionalFormatting sqref="J43:K48">
     <cfRule type="expression" dxfId="18" priority="100" stopIfTrue="1">
@@ -6733,24 +6733,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17" t="s">
+      <c r="C1" s="42"/>
+      <c r="D1" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="42"/>
+      <c r="H1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
